--- a/p6_deployment/data/england/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF45"/>
+  <dimension ref="A1:BF47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -722,23 +722,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45523.66666666666</v>
       </c>
       <c r="C2" t="n">
         <v>157</v>
       </c>
       <c r="D2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2" t="n">
-        <v>755</v>
+        <v>259</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>372</v>
       </c>
       <c r="G2" t="n">
         <v>48</v>
@@ -760,125 +760,125 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.7333333333333329</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
         <v>-1</v>
       </c>
-      <c r="O2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.8949999999999998</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.085</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-3.5</v>
-      </c>
+      <c r="AG2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>77.95454545454545</v>
+        <v>71.22727272727272</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.54545454545455</v>
+        <v>77.21818181818182</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2.630632463511716</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>1.710131649682733</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.750895061728386</v>
+      </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>-2170909.090909095</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.8393939393939434</v>
-      </c>
+        <v>1.416574074074074</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-1496606.229626353</v>
+        <v>-4.901921991550481</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01515151515153</v>
+        <v>-1.124675669044819</v>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>-1.594456852916604</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>-30074135.80246913</v>
+      </c>
       <c r="AW2" t="n">
-        <v>0.1758826805576206</v>
+        <v>-21386852.84656792</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.002566178518194</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.05421761102101685</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.6666666666666679</v>
-      </c>
+        <v>-5.814135802469153</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>0.3818181818181756</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="n">
-        <v>-0.2636363636363639</v>
-      </c>
+        <v>-0.2725935177367069</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-6.836882716049388</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.7213271604938272</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-5.786652515870784</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -886,23 +886,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45522.52083333334</v>
       </c>
       <c r="C3" t="n">
         <v>157</v>
       </c>
       <c r="D3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="G3" t="n">
         <v>48</v>
@@ -924,125 +924,125 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>293</v>
+        <v>423</v>
       </c>
       <c r="M3" t="n">
-        <v>61</v>
+        <v>271</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>6.5</v>
+        <v>-4.333333333333336</v>
       </c>
       <c r="T3" t="n">
-        <v>-4</v>
+        <v>4.333333333333336</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9299999999999998</v>
+        <v>2.083333333333334</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.285</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="W3" t="n">
-        <v>12.5</v>
+        <v>0.5366666666666666</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0.8383333333333336</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>3.166666666666666</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.5</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2.5</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>77.62272727272727</v>
+        <v>78.76801346801348</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.5</v>
+        <v>77.85696969696968</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3.136223368135148</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>-1.560371935855681</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.8600168350168076</v>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-7819999.999999996</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-1.345454545454544</v>
-      </c>
+        <v>-3.155808080808079</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-2737930.412316443</v>
+        <v>-6.906925140326337</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.309090909090855</v>
+        <v>4.734041241776936</v>
       </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>3.450909090909093</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-51974579.12457912</v>
+      </c>
       <c r="AW3" t="n">
-        <v>0.290929674900255</v>
+        <v>-29818279.90304367</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1.394916815210919</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.09636257533316339</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.690909090909091</v>
-      </c>
+        <v>-7.229292929292924</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-0.9636363636363683</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
-        <v>-0.01818181818181852</v>
-      </c>
+        <v>-0.6003593821898774</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-4.165824915824913</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1.368686868686869</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-3.783660279230858</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1050,11 +1050,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C4" t="n">
         <v>157</v>
@@ -1063,10 +1063,10 @@
         <v>146</v>
       </c>
       <c r="E4" t="n">
-        <v>524</v>
+        <v>755</v>
       </c>
       <c r="F4" t="n">
-        <v>554</v>
+        <v>134</v>
       </c>
       <c r="G4" t="n">
         <v>48</v>
@@ -1088,125 +1088,125 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>311</v>
+        <v>389</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="O4" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>-11.33333333333333</v>
+        <v>-12</v>
       </c>
       <c r="U4" t="n">
-        <v>2.831666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.891666666666667</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>22.66666666666667</v>
+        <v>-0.8949999999999998</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.66666666666667</v>
+        <v>1.085</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.833333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.166666666666667</v>
+        <v>-3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-1</v>
       </c>
-      <c r="AD4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>18.33333333333334</v>
-      </c>
       <c r="AF4" t="n">
-        <v>-18.33333333333334</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.333333333333334</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>75.97205387205388</v>
+        <v>77.95454545454545</v>
       </c>
       <c r="AL4" t="n">
-        <v>84.92727272727274</v>
+        <v>76.54545454545455</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1.514809081527346</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>-1.85137343987515</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.9303030303030084</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>47974942.12962963</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.856481481481467</v>
-      </c>
+        <v>0.262626262626263</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>28676257.99123477</v>
+        <v>0.8422794147322605</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.7152777777777999</v>
+        <v>-3.644003838928569</v>
       </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="n">
-        <v>0.1099439775910405</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>-2567373.737373738</v>
+      </c>
       <c r="AW4" t="n">
-        <v>8.728974173401411</v>
+        <v>590628.4114840962</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.860380898770984</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.4756758205674614</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-1.576388888888893</v>
-      </c>
+        <v>-0.0929292929292842</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>7.224537037037038</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
-        <v>0.8449074074074074</v>
-      </c>
+        <v>-0.05880993807812152</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.9282828282828177</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.2494949494949499</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.319430534100235</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1214,11 +1214,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45521.5625</v>
       </c>
       <c r="C5" t="n">
         <v>157</v>
@@ -1227,10 +1227,10 @@
         <v>146</v>
       </c>
       <c r="E5" t="n">
-        <v>253</v>
+        <v>158</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>396</v>
       </c>
       <c r="G5" t="n">
         <v>48</v>
@@ -1252,125 +1252,125 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="M5" t="n">
-        <v>271</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.75</v>
+        <v>-4</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.75</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.24</v>
+        <v>6.5</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1925</v>
+        <v>-4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.9299999999999998</v>
       </c>
       <c r="X5" t="n">
-        <v>-3</v>
+        <v>-1.285</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-14.75</v>
-      </c>
       <c r="AF5" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>-1.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>77.02146464646464</v>
+        <v>77.62272727272727</v>
       </c>
       <c r="AL5" t="n">
-        <v>75.80000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.780269834859922</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>3.932435117217729</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.4767676767676505</v>
+      </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>2198398.989898991</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.8389898989899081</v>
-      </c>
+        <v>1.720202020202024</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>-862436.9560944131</v>
+        <v>-0.23545468179951</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.486262626262658</v>
+        <v>-2.211052703177643</v>
       </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>1.574166821572263</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-7140101.010101002</v>
+      </c>
       <c r="AW5" t="n">
-        <v>-0.3981130362137151</v>
+        <v>-5597251.616995063</v>
       </c>
       <c r="AX5" t="n">
-        <v>-3.195366186138841</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.007269238740499784</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.432525252525249</v>
-      </c>
+        <v>-0.686868686868678</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>1.210909090909112</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>0.2260606060606059</v>
-      </c>
+        <v>0.003607611248276132</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1.246464646464659</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.002020202020202255</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-2.078770594755241</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1378,7 +1378,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1391,10 +1391,10 @@
         <v>146</v>
       </c>
       <c r="E6" t="n">
-        <v>624</v>
+        <v>524</v>
       </c>
       <c r="F6" t="n">
-        <v>419</v>
+        <v>554</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -1416,125 +1416,125 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>389</v>
+        <v>311</v>
       </c>
       <c r="M6" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>18.33333333333334</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2999999999999998</v>
+        <v>-18.33333333333334</v>
       </c>
       <c r="U6" t="n">
-        <v>1.316</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3799999999999999</v>
+        <v>-11.33333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>7.199999999999999</v>
+        <v>2.831666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>1.800000000000001</v>
+        <v>-2.891666666666667</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>-1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.6000000000000001</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.8999999999999999</v>
+        <v>-1</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.5</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.25</v>
+        <v>-3</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-2.199999999999999</v>
-      </c>
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-21.66666666666667</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
-        <v>73.29545454545455</v>
+        <v>75.97205387205388</v>
       </c>
       <c r="AL6" t="n">
-        <v>72.99111111111111</v>
+        <v>84.92727272727274</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.791992086689731</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>0.6395235638114904</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.06126543209876445</v>
+      </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>14857121.21212121</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4.874675324675309</v>
-      </c>
+        <v>-1.92546296296296</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>12180272.34625734</v>
+        <v>9.422332167316682</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.000216450216442</v>
+        <v>-1.619370730748443</v>
       </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="n">
-        <v>1.614797585700945</v>
-      </c>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>46122029.32098766</v>
+      </c>
       <c r="AW6" t="n">
-        <v>4.436560058806137</v>
+        <v>29354422.66539789</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.942932897796808</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.4727272727272727</v>
-      </c>
+        <v>6.808487654320999</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>4.967316017316037</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
-        <v>0.5060606060606059</v>
-      </c>
+        <v>0.4937788767819729</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.745061728395044</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.7885802469135799</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.836109123075062</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1542,7 +1542,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1555,10 +1555,10 @@
         <v>146</v>
       </c>
       <c r="E7" t="n">
-        <v>392</v>
+        <v>253</v>
       </c>
       <c r="F7" t="n">
-        <v>312</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>48</v>
@@ -1580,125 +1580,125 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>145</v>
+        <v>311</v>
       </c>
       <c r="M7" t="n">
-        <v>403</v>
+        <v>271</v>
       </c>
       <c r="N7" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>-3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.0349999999999997</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.4700000000000002</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-2.75</v>
-      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
-        <v>81.76666666666667</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AL7" t="n">
-        <v>80.13415404040404</v>
+        <v>75.80000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.761489450459663</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>1.850529250983385</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.802918069584734</v>
+      </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-0.3366666666666731</v>
-      </c>
+        <v>1.552300785634117</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>-131404.7277834453</v>
+        <v>-0.003630135120403111</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.443333333333328</v>
+        <v>8.059273693077529</v>
       </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>0.89531110384657</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>1861301.907968573</v>
+      </c>
       <c r="AW7" t="n">
-        <v>1.189468632054457</v>
+        <v>-1243673.984887624</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.6277514713441406</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.1143020154690639</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.533333333333335</v>
-      </c>
+        <v>1.206846240179587</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>0.3599999999999994</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
-        <v>0.1133333333333333</v>
-      </c>
+        <v>-0.0007441557858842707</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.9500561167227914</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.2061728395061724</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-3.187342346168066</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1706,11 +1706,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.35416666666</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C8" t="n">
         <v>157</v>
@@ -1719,10 +1719,10 @@
         <v>146</v>
       </c>
       <c r="E8" t="n">
-        <v>701</v>
+        <v>624</v>
       </c>
       <c r="F8" t="n">
-        <v>585</v>
+        <v>419</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -1744,119 +1744,125 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>346</v>
+        <v>389</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="N8" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>-4</v>
+        <v>-2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1925000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3675</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="W8" t="n">
-        <v>4.25</v>
+        <v>1.316</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.5</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>-2</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.25</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="AE8" t="n">
-        <v>-4</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK8" t="inlineStr"/>
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>73.29545454545455</v>
+      </c>
       <c r="AL8" t="n">
-        <v>78.65909090909091</v>
+        <v>72.99111111111111</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.01798654244305453</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>1.187496107898919</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5.630505050505064</v>
+      </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>-46767121.2121212</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-11.44696969696969</v>
-      </c>
+        <v>0.9371950271950311</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>-33372580.22774327</v>
+        <v>2.316979761500221</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.4075757575757279</v>
+        <v>2.569776904680964</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="n">
-        <v>1.849767080745345</v>
-      </c>
-      <c r="AV8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>14679362.08236209</v>
+      </c>
       <c r="AW8" t="n">
-        <v>-10.85770358868186</v>
+        <v>8456518.499563098</v>
       </c>
       <c r="AX8" t="n">
-        <v>-10.96079192546583</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.9254227053140098</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.5378787878787854</v>
-      </c>
+        <v>4.997785547785554</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>-12.18787878787877</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
-        <v>-1.703030303030303</v>
-      </c>
+        <v>0.3882900432900431</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.616324786324782</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.5293939393939393</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.443425715375852</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1864,11 +1870,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45520.66666666666</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C9" t="n">
         <v>157</v>
@@ -1877,10 +1883,10 @@
         <v>146</v>
       </c>
       <c r="E9" t="n">
-        <v>639</v>
+        <v>392</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>312</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1902,125 +1908,125 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="M9" t="n">
-        <v>124</v>
+        <v>403</v>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>-8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8125</v>
+        <v>-1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.08499999999999996</v>
+        <v>-1</v>
       </c>
       <c r="W9" t="n">
-        <v>5.25</v>
+        <v>-0.0349999999999997</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>-0.4700000000000002</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Z9" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA9" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.75</v>
-      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="n">
-        <v>78.10954545454544</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>74.54545454545453</v>
+        <v>80.13415404040404</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.867495183844255</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>0.9373982822216078</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.584444444444415</v>
+      </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>16324914.14141415</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5.424368686868689</v>
-      </c>
+        <v>0.8288888888888906</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>11235910.75182543</v>
+        <v>0.7075875852733304</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.9743686868686439</v>
+        <v>2.056395486944524</v>
       </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
-        <v>-3.807347578359405</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>19666.66666666605</v>
+      </c>
       <c r="AW9" t="n">
-        <v>-0.1084503027166051</v>
+        <v>-534417.4824704174</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.024850962123978</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.4951040317312698</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-2.043282828282827</v>
-      </c>
+        <v>-0.1055555555555543</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>2.931060606060598</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>0.6678787878787877</v>
-      </c>
+        <v>0.1306318391952392</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.2422222222222388</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.118888888888889</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.007013003037698695</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -2028,11 +2034,11 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45518.66666666666</v>
+        <v>45521.35416666666</v>
       </c>
       <c r="C10" t="n">
         <v>157</v>
@@ -2041,19 +2047,19 @@
         <v>146</v>
       </c>
       <c r="E10" t="n">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>585</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2062,129 +2068,123 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>73</v>
+        <v>346</v>
       </c>
       <c r="M10" t="n">
-        <v>427</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.333333333333333</v>
+        <v>-4</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3266666666666667</v>
+        <v>-2.25</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.066666666666667</v>
+        <v>-4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.666666666666666</v>
+        <v>-0.1925000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.333333333333333</v>
+        <v>-1.3675</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.333333333333333</v>
+        <v>-3.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>-2</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>5.666666666666664</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-5.666666666666664</v>
-      </c>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="n">
-        <v>6.666666666666668</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>72.98888888888888</v>
-      </c>
+      <c r="AG10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>69</v>
+        <v>78.65909090909091</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.02683966861602016</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>1.856644212032641</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.7672727272727116</v>
+      </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>6390370.370370369</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>5.096296296296288</v>
-      </c>
+        <v>0.6181818181818137</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>3713837.719298245</v>
+        <v>-10.55549400194862</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.455555555555605</v>
+        <v>-0.2009810010960678</v>
       </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="n">
-        <v>1.793689083820663</v>
-      </c>
-      <c r="AV10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-44092090.90909091</v>
+      </c>
       <c r="AW10" t="n">
-        <v>6.535148635477583</v>
+        <v>-32198919.6352454</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.317750974658864</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.00164473684210531</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.8407407407407419</v>
-      </c>
+        <v>-11.91727272727273</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
-        <v>5.207407407407402</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
-        <v>0.1666666666666665</v>
-      </c>
+        <v>-0.8132648276701988</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-11.20681818181816</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-1.621818181818182</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-11.09582914687613</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
@@ -2192,11 +2192,11 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45520.66666666666</v>
       </c>
       <c r="C11" t="n">
         <v>157</v>
@@ -2205,19 +2205,19 @@
         <v>146</v>
       </c>
       <c r="E11" t="n">
-        <v>347</v>
+        <v>639</v>
       </c>
       <c r="F11" t="n">
-        <v>596</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -2226,125 +2226,129 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>428</v>
+        <v>293</v>
       </c>
       <c r="M11" t="n">
-        <v>236</v>
+        <v>124</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.08499999999999996</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>3.5</v>
       </c>
-      <c r="T11" t="n">
-        <v>8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="n">
-        <v>71.18181818181819</v>
+        <v>77.9919696969697</v>
       </c>
       <c r="AL11" t="n">
-        <v>69.5409090909091</v>
+        <v>74.54545454545453</v>
       </c>
       <c r="AM11" t="n">
-        <v>-4.871307291032338</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>-3.82273049426183</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.772474747474746</v>
+      </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>1762272.727272727</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>4.716666666666669</v>
-      </c>
+        <v>-2.187542087542088</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>1835970.306600901</v>
+        <v>0.3442508678921712</v>
       </c>
       <c r="AS11" t="n">
-        <v>-2.096969696969666</v>
+        <v>2.684438527277422</v>
       </c>
       <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="n">
-        <v>-0.7349977672228327</v>
-      </c>
-      <c r="AV11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>16866637.20538721</v>
+      </c>
       <c r="AW11" t="n">
-        <v>3.686903747006042</v>
+        <v>12046064.33408343</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.701822758088753</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.01249999999999996</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.16363636363636</v>
-      </c>
+        <v>2.726262626262638</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
-        <v>1.980303030303034</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
-        <v>0.09090909090909105</v>
-      </c>
+        <v>0.5558858743321657</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.328535353535358</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.6883838383838383</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.367332947671812</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
@@ -2352,23 +2356,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45518.66666666666</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>146</v>
       </c>
       <c r="E12" t="n">
-        <v>419</v>
+        <v>691</v>
       </c>
       <c r="F12" t="n">
-        <v>567</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -2390,58 +2394,124 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>428</v>
+        <v>73</v>
       </c>
       <c r="M12" t="n">
-        <v>429</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+        <v>427</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.3266666666666667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.066666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-7.333333333333333</v>
+      </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+        <v>72.98888888888888</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>69</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.537110809082559</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.31852617079889</v>
+      </c>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>-1.11623048668503</v>
+      </c>
       <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>7.334945108426126</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.362754095319872</v>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>6015646.235078054</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3510151.26442937</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.410445362718065</v>
+      </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>0.06099221985444903</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.632380624426091</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.1529958677685948</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.212224376930266</v>
+      </c>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2450,23 +2520,23 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45517.66666666666</v>
+        <v>45518.65625</v>
       </c>
       <c r="C13" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D13" t="n">
         <v>146</v>
       </c>
       <c r="E13" t="n">
-        <v>277</v>
+        <v>419</v>
       </c>
       <c r="F13" t="n">
-        <v>227</v>
+        <v>567</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2488,23 +2558,15 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>110</v>
+        <v>428</v>
       </c>
       <c r="M13" t="n">
-        <v>429</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2527,7 +2589,7 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="n">
-        <v>76.57205387205387</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -2556,23 +2618,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C14" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
       </c>
       <c r="E14" t="n">
-        <v>729</v>
+        <v>347</v>
       </c>
       <c r="F14" t="n">
-        <v>699</v>
+        <v>596</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -2594,60 +2656,124 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M14" t="n">
-        <v>429</v>
+        <v>236</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>8</v>
+      </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AK14" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>69.5409090909091</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.083286126447355</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-3.375252525252478</v>
+      </c>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>-2.49267676767677</v>
+      </c>
       <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>3.658565308168363</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-4.083728128932705</v>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>1897077.02020202</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1286850.884526516</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.596212121212119</v>
+      </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>0.005927050771999509</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.459595959595973</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.09393939393939421</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.174513595695927</v>
+      </c>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
         <v>0</v>
@@ -2656,23 +2782,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" t="n">
         <v>146</v>
       </c>
       <c r="E15" t="n">
-        <v>399</v>
+        <v>277</v>
       </c>
       <c r="F15" t="n">
-        <v>542</v>
+        <v>227</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -2694,15 +2820,23 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M15" t="n">
         <v>430</v>
       </c>
-      <c r="M15" t="n">
-        <v>429</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2724,7 +2858,9 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>76.57205387205387</v>
+      </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
@@ -2752,23 +2888,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C16" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D16" t="n">
         <v>146</v>
       </c>
       <c r="E16" t="n">
-        <v>781</v>
+        <v>245</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>441</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -2790,10 +2926,10 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>418</v>
+      </c>
+      <c r="M16" t="n">
         <v>430</v>
-      </c>
-      <c r="M16" t="n">
-        <v>168</v>
       </c>
       <c r="N16" t="n">
         <v>-2</v>
@@ -2824,10 +2960,10 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AK16" t="n">
+        <v>69.13636363636363</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
@@ -2854,23 +2990,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C17" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D17" t="n">
         <v>146</v>
       </c>
       <c r="E17" t="n">
-        <v>740</v>
+        <v>566</v>
       </c>
       <c r="F17" t="n">
-        <v>412</v>
+        <v>540</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -2892,16 +3028,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>331</v>
+        <v>431</v>
       </c>
       <c r="M17" t="n">
-        <v>236</v>
+        <v>430</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="n">
         <v>-1</v>
@@ -2912,105 +3048,45 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="n">
-        <v>-5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>74</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>69</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-0.3179805865900676</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="n">
-        <v>-913171.2962962962</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-4.75833333333334</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-113208.6218672572</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.131481481481472</v>
-      </c>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="n">
-        <v>0.8968506802670184</v>
-      </c>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="n">
-        <v>0.6488685481820511</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>-0.3063794040372159</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.047222222222217</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0.9592592592592553</v>
-      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
@@ -3018,23 +3094,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C18" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D18" t="n">
         <v>146</v>
       </c>
       <c r="E18" t="n">
-        <v>245</v>
+        <v>740</v>
       </c>
       <c r="F18" t="n">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -3056,62 +3132,124 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>418</v>
+        <v>331</v>
       </c>
       <c r="M18" t="n">
-        <v>429</v>
+        <v>236</v>
       </c>
       <c r="N18" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1</v>
+      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>-21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>21</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>9</v>
+      </c>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="n">
-        <v>69.13636363636363</v>
-      </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>69</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.018441460376287</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.117245370370341</v>
+      </c>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>4.656327160493827</v>
+      </c>
       <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0.3003679171335136</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.5588051963200087</v>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>-1287210.648148148</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-109708.5345255611</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.2523148148148096</v>
+      </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-5.889969135802474</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.4068603831073148</v>
+      </c>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
         <v>0</v>
@@ -3120,23 +3258,23 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C19" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D19" t="n">
         <v>146</v>
       </c>
       <c r="E19" t="n">
-        <v>566</v>
+        <v>729</v>
       </c>
       <c r="F19" t="n">
-        <v>540</v>
+        <v>699</v>
       </c>
       <c r="G19" t="n">
         <v>48</v>
@@ -3158,23 +3296,19 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>431</v>
+      </c>
+      <c r="M19" t="n">
         <v>430</v>
       </c>
-      <c r="M19" t="n">
-        <v>429</v>
-      </c>
       <c r="N19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3224,23 +3358,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C20" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D20" t="n">
         <v>146</v>
       </c>
       <c r="E20" t="n">
-        <v>182</v>
+        <v>781</v>
       </c>
       <c r="F20" t="n">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="G20" t="n">
         <v>48</v>
@@ -3262,23 +3396,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M20" t="n">
-        <v>429</v>
+        <v>168</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3301,7 +3431,9 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
+      <c r="AL20" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
@@ -3335,7 +3467,7 @@
         <v>45517.65625</v>
       </c>
       <c r="C21" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D21" t="n">
         <v>146</v>
@@ -3366,10 +3498,10 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>431</v>
+      </c>
+      <c r="M21" t="n">
         <v>430</v>
-      </c>
-      <c r="M21" t="n">
-        <v>429</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -3435,7 +3567,7 @@
         <v>45517.65625</v>
       </c>
       <c r="C22" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D22" t="n">
         <v>146</v>
@@ -3469,7 +3601,7 @@
         <v>374</v>
       </c>
       <c r="M22" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -3530,23 +3662,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C23" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D23" t="n">
         <v>146</v>
       </c>
       <c r="E23" t="n">
-        <v>555</v>
+        <v>399</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>542</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -3568,23 +3700,15 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>431</v>
+      </c>
+      <c r="M23" t="n">
         <v>430</v>
       </c>
-      <c r="M23" t="n">
-        <v>429</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -3634,23 +3758,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C24" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" t="n">
         <v>146</v>
       </c>
       <c r="E24" t="n">
-        <v>387</v>
+        <v>555</v>
       </c>
       <c r="F24" t="n">
-        <v>501</v>
+        <v>83</v>
       </c>
       <c r="G24" t="n">
         <v>48</v>
@@ -3672,22 +3796,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>347</v>
+        <v>431</v>
       </c>
       <c r="M24" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N24" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3710,9 +3834,7 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
@@ -3747,7 +3869,7 @@
         <v>45517.65625</v>
       </c>
       <c r="C25" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D25" t="n">
         <v>146</v>
@@ -3778,10 +3900,10 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>431</v>
+      </c>
+      <c r="M25" t="n">
         <v>430</v>
-      </c>
-      <c r="M25" t="n">
-        <v>429</v>
       </c>
       <c r="N25" t="n">
         <v>1</v>
@@ -3840,23 +3962,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C26" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D26" t="n">
         <v>146</v>
       </c>
       <c r="E26" t="n">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="F26" t="n">
-        <v>125</v>
+        <v>501</v>
       </c>
       <c r="G26" t="n">
         <v>48</v>
@@ -3878,19 +4000,23 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="M26" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1</v>
+      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -3913,7 +4039,7 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="n">
-        <v>70.70833333333333</v>
+        <v>69.64141414141415</v>
       </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
@@ -3942,23 +4068,23 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C27" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D27" t="n">
         <v>146</v>
       </c>
       <c r="E27" t="n">
-        <v>540</v>
+        <v>182</v>
       </c>
       <c r="F27" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -3980,15 +4106,23 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>431</v>
+      </c>
+      <c r="M27" t="n">
         <v>430</v>
       </c>
-      <c r="M27" t="n">
-        <v>429</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4038,23 +4172,23 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C28" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D28" t="n">
         <v>146</v>
       </c>
       <c r="E28" t="n">
-        <v>684</v>
+        <v>540</v>
       </c>
       <c r="F28" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -4076,10 +4210,10 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>431</v>
+      </c>
+      <c r="M28" t="n">
         <v>430</v>
-      </c>
-      <c r="M28" t="n">
-        <v>333</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -4107,9 +4241,7 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
@@ -4136,23 +4268,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C29" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D29" t="n">
         <v>146</v>
       </c>
       <c r="E29" t="n">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="F29" t="n">
-        <v>473</v>
+        <v>125</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -4174,13 +4306,17 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>73</v>
+      </c>
+      <c r="M29" t="n">
         <v>430</v>
       </c>
-      <c r="M29" t="n">
-        <v>429</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
@@ -4204,7 +4340,9 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
+      <c r="AK29" t="n">
+        <v>70.70833333333333</v>
+      </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
@@ -4232,23 +4370,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C30" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D30" t="n">
         <v>146</v>
       </c>
       <c r="E30" t="n">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="F30" t="n">
-        <v>368</v>
+        <v>194</v>
       </c>
       <c r="G30" t="n">
         <v>48</v>
@@ -4270,56 +4408,124 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="M30" t="n">
-        <v>429</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>21</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-21</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-24</v>
+      </c>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
+      <c r="AK30" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.481839318662072</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-1.653888888888872</v>
+      </c>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
+      <c r="AP30" t="n">
+        <v>-0.617986111111108</v>
+      </c>
       <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>-2.218100666103766</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.2448807569279836</v>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
+      <c r="AV30" t="n">
+        <v>-2184951.388888889</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>-1374683.396464646</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>-2.831736111111098</v>
+      </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
-      <c r="BD30" t="inlineStr"/>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>-2.584305555555559</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>-2.872966736136249</v>
+      </c>
       <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="n">
         <v>0</v>
@@ -4328,23 +4534,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C31" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D31" t="n">
         <v>146</v>
       </c>
       <c r="E31" t="n">
-        <v>309</v>
+        <v>684</v>
       </c>
       <c r="F31" t="n">
-        <v>687</v>
+        <v>139</v>
       </c>
       <c r="G31" t="n">
         <v>48</v>
@@ -4366,10 +4572,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M31" t="n">
-        <v>429</v>
+        <v>333</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -4397,7 +4603,9 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>72.22962962962963</v>
+      </c>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
@@ -4424,23 +4632,23 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C32" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D32" t="n">
         <v>146</v>
       </c>
       <c r="E32" t="n">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="F32" t="n">
-        <v>194</v>
+        <v>368</v>
       </c>
       <c r="G32" t="n">
         <v>48</v>
@@ -4462,125 +4670,57 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="M32" t="n">
-        <v>209</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>4</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>-6</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V32" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="W32" t="n">
-        <v>7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>-24</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-21</v>
-      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>70.18181818181819</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>-1.610778081567503</v>
-      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="n">
-        <v>-2171296.296296297</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>-2.606111111111105</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>-1147986.386420596</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>-0.975555555555502</v>
-      </c>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="n">
-        <v>1.610061517429937</v>
-      </c>
+      <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="n">
-        <v>-1.164470266575535</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>-2.090940419229881</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>-0.7666666666666693</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>-2.892777777777781</v>
-      </c>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="n">
         <v>0</v>
       </c>
@@ -4588,23 +4728,23 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C33" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D33" t="n">
         <v>146</v>
       </c>
       <c r="E33" t="n">
-        <v>621</v>
+        <v>309</v>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>687</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -4626,10 +4766,10 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>431</v>
+      </c>
+      <c r="M33" t="n">
         <v>430</v>
-      </c>
-      <c r="M33" t="n">
-        <v>429</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -4684,23 +4824,23 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D34" t="n">
         <v>146</v>
       </c>
       <c r="E34" t="n">
-        <v>590</v>
+        <v>764</v>
       </c>
       <c r="F34" t="n">
-        <v>600</v>
+        <v>790</v>
       </c>
       <c r="G34" t="n">
         <v>48</v>
@@ -4722,10 +4862,10 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>346</v>
+      </c>
+      <c r="M34" t="n">
         <v>430</v>
-      </c>
-      <c r="M34" t="n">
-        <v>209</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -4752,10 +4892,10 @@
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="n">
-        <v>71.77777777777777</v>
-      </c>
+      <c r="AK34" t="n">
+        <v>69.33522727272728</v>
+      </c>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
@@ -4789,7 +4929,7 @@
         <v>45517.65625</v>
       </c>
       <c r="C35" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D35" t="n">
         <v>146</v>
@@ -4820,10 +4960,10 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>431</v>
+      </c>
+      <c r="M35" t="n">
         <v>430</v>
-      </c>
-      <c r="M35" t="n">
-        <v>429</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -4878,23 +5018,23 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C36" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D36" t="n">
         <v>146</v>
       </c>
       <c r="E36" t="n">
-        <v>504</v>
+        <v>621</v>
       </c>
       <c r="F36" t="n">
-        <v>353</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -4916,17 +5056,13 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>431</v>
+      </c>
+      <c r="M36" t="n">
         <v>430</v>
       </c>
-      <c r="M36" t="n">
-        <v>175</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
@@ -4951,9 +5087,7 @@
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="n">
-        <v>67.40000000000001</v>
-      </c>
+      <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
@@ -4980,23 +5114,23 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C37" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D37" t="n">
         <v>146</v>
       </c>
       <c r="E37" t="n">
-        <v>756</v>
+        <v>228</v>
       </c>
       <c r="F37" t="n">
-        <v>181</v>
+        <v>488</v>
       </c>
       <c r="G37" t="n">
         <v>48</v>
@@ -5018,16 +5152,16 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>431</v>
+      </c>
+      <c r="M37" t="n">
         <v>430</v>
       </c>
-      <c r="M37" t="n">
-        <v>429</v>
-      </c>
       <c r="N37" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -5080,23 +5214,23 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C38" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D38" t="n">
         <v>146</v>
       </c>
       <c r="E38" t="n">
-        <v>764</v>
+        <v>590</v>
       </c>
       <c r="F38" t="n">
-        <v>790</v>
+        <v>600</v>
       </c>
       <c r="G38" t="n">
         <v>48</v>
@@ -5118,10 +5252,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="M38" t="n">
-        <v>429</v>
+        <v>209</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -5148,10 +5282,10 @@
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="n">
-        <v>69.33522727272728</v>
-      </c>
-      <c r="AL38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
@@ -5178,23 +5312,23 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C39" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D39" t="n">
         <v>146</v>
       </c>
       <c r="E39" t="n">
-        <v>325</v>
+        <v>528</v>
       </c>
       <c r="F39" t="n">
-        <v>759</v>
+        <v>191</v>
       </c>
       <c r="G39" t="n">
         <v>48</v>
@@ -5216,16 +5350,16 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>418</v>
+      </c>
+      <c r="M39" t="n">
         <v>430</v>
       </c>
-      <c r="M39" t="n">
-        <v>429</v>
-      </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -5250,7 +5384,9 @@
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
+      <c r="AK39" t="n">
+        <v>71.47727272727272</v>
+      </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
@@ -5278,23 +5414,23 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C40" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D40" t="n">
         <v>146</v>
       </c>
       <c r="E40" t="n">
-        <v>228</v>
+        <v>504</v>
       </c>
       <c r="F40" t="n">
-        <v>488</v>
+        <v>353</v>
       </c>
       <c r="G40" t="n">
         <v>48</v>
@@ -5316,16 +5452,16 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M40" t="n">
-        <v>429</v>
+        <v>175</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -5351,7 +5487,9 @@
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
+      <c r="AL40" t="n">
+        <v>67.40000000000001</v>
+      </c>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
@@ -5378,23 +5516,23 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C41" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D41" t="n">
         <v>146</v>
       </c>
       <c r="E41" t="n">
-        <v>528</v>
+        <v>756</v>
       </c>
       <c r="F41" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G41" t="n">
         <v>48</v>
@@ -5416,16 +5554,16 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="M41" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N41" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O41" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -5450,9 +5588,7 @@
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
@@ -5480,23 +5616,23 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C42" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D42" t="n">
         <v>146</v>
       </c>
       <c r="E42" t="n">
-        <v>483</v>
+        <v>325</v>
       </c>
       <c r="F42" t="n">
-        <v>537</v>
+        <v>759</v>
       </c>
       <c r="G42" t="n">
         <v>48</v>
@@ -5518,13 +5654,17 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>431</v>
+      </c>
+      <c r="M42" t="n">
         <v>430</v>
       </c>
-      <c r="M42" t="n">
-        <v>221</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
@@ -5549,9 +5689,7 @@
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
@@ -5578,23 +5716,23 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C43" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D43" t="n">
         <v>146</v>
       </c>
       <c r="E43" t="n">
-        <v>217</v>
+        <v>293</v>
       </c>
       <c r="F43" t="n">
-        <v>74</v>
+        <v>473</v>
       </c>
       <c r="G43" t="n">
         <v>48</v>
@@ -5616,10 +5754,10 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>431</v>
+      </c>
+      <c r="M43" t="n">
         <v>430</v>
-      </c>
-      <c r="M43" t="n">
-        <v>278</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -5647,9 +5785,7 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="n">
-        <v>76</v>
-      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
@@ -5676,23 +5812,23 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
       <c r="C44" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D44" t="n">
         <v>146</v>
       </c>
       <c r="E44" t="n">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="F44" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="G44" t="n">
         <v>48</v>
@@ -5714,17 +5850,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M44" t="n">
-        <v>429</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
@@ -5749,7 +5881,9 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
+      <c r="AL44" t="n">
+        <v>76</v>
+      </c>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
@@ -5776,29 +5910,29 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C45" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D45" t="n">
         <v>146</v>
       </c>
       <c r="E45" t="n">
-        <v>639</v>
+        <v>244</v>
       </c>
       <c r="F45" t="n">
-        <v>424</v>
+        <v>152</v>
       </c>
       <c r="G45" t="n">
         <v>48</v>
       </c>
       <c r="H45" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -5810,130 +5944,328 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fa community shield</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293</v>
+        <v>431</v>
       </c>
       <c r="M45" t="n">
-        <v>271</v>
+        <v>430</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
-      </c>
-      <c r="P45" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-4</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="n">
-        <v>2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.1174999999999999</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.5950000000000002</v>
-      </c>
-      <c r="W45" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="X45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>7</v>
-      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>76.15625</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>77.36540404040404</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>5.976728453238991</v>
-      </c>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="n">
-        <v>-46160858.58585859</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>-3.410858585858577</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>-26308142.17514245</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.386868686868638</v>
-      </c>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="n">
-        <v>-0.4983721947276933</v>
-      </c>
+      <c r="AU45" t="inlineStr"/>
       <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="n">
-        <v>-5.795527952617149</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>-3.781344512442644</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>-0.5157635798060989</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>-2.023737373737372</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>-5.946212121212142</v>
-      </c>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr"/>
       <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="n">
-        <v>-1.022348484848485</v>
-      </c>
+      <c r="BE45" t="inlineStr"/>
       <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C46" t="n">
+        <v>157</v>
+      </c>
+      <c r="D46" t="n">
+        <v>146</v>
+      </c>
+      <c r="E46" t="n">
+        <v>483</v>
+      </c>
+      <c r="F46" t="n">
+        <v>537</v>
+      </c>
+      <c r="G46" t="n">
+        <v>48</v>
+      </c>
+      <c r="H46" t="n">
+        <v>484</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>431</v>
+      </c>
+      <c r="M46" t="n">
+        <v>221</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C47" t="n">
+        <v>157</v>
+      </c>
+      <c r="D47" t="n">
+        <v>146</v>
+      </c>
+      <c r="E47" t="n">
+        <v>639</v>
+      </c>
+      <c r="F47" t="n">
+        <v>424</v>
+      </c>
+      <c r="G47" t="n">
+        <v>48</v>
+      </c>
+      <c r="H47" t="n">
+        <v>482</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fa community shield</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>293</v>
+      </c>
+      <c r="M47" t="n">
+        <v>271</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T47" t="n">
+        <v>7</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.1174999999999999</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.5950000000000002</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="n">
+        <v>76.15625</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>77.36540404040404</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>-0.3707263230281157</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>2.906565656565647</v>
+      </c>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="n">
+        <v>-1.729208754208756</v>
+      </c>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="n">
+        <v>-4.997674767096129</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>5.760937278951985</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="n">
+        <v>-43387504.2087542</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>-25716382.34990418</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>-5.511616161616161</v>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="n">
+        <v>-0.4099647291942687</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>-3.101262626262624</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>-0.9106060606060611</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>-3.458909711227491</v>
+      </c>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="n">
         <v>1</v>
       </c>
     </row>

--- a/p6_deployment/data/england/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_tagged.xlsx
@@ -495,24 +495,24 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -769,28 +769,28 @@
         <v>-3</v>
       </c>
       <c r="O2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="P2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-10.5</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="T2" t="n">
-        <v>10.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>-5.333333333333333</v>
+        <v>-7.666666666666666</v>
       </c>
       <c r="W2" t="n">
         <v>-0.7333333333333329</v>
@@ -799,16 +799,16 @@
         <v>-0.8333333333333335</v>
       </c>
       <c r="Y2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.1666666666666661</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>-5.333333333333334</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.666666666666667</v>
       </c>
       <c r="AC2" t="n">
         <v>0.5</v>
@@ -817,16 +817,16 @@
         <v>-0.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.8333333333333333</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>-1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-7.666666666666666</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
@@ -836,49 +836,49 @@
       <c r="AL2" t="n">
         <v>77.21818181818182</v>
       </c>
-      <c r="AM2" t="n">
-        <v>1.710131649682733</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-1.750895061728386</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>-5.786111111111126</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-29846130.95238096</v>
+      </c>
       <c r="AP2" t="n">
-        <v>1.416574074074074</v>
+        <v>-6.928968253968279</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>-4.901921991550481</v>
-      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-1.124675669044819</v>
+        <v>-0.6529583972743467</v>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>-0.6529761904761904</v>
+      </c>
       <c r="AV2" t="n">
-        <v>-30074135.80246913</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-21386852.84656792</v>
-      </c>
+        <v>1.610714285714284</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-5.814135802469153</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>-0.2725935177367069</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-6.836882716049388</v>
-      </c>
+        <v>1.697725122744469</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-2.036111111111097</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.2652031356801094</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-0.7213271604938272</v>
+        <v>-4.617364768874054</v>
       </c>
       <c r="BD2" t="n">
-        <v>-5.786652515870784</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>-5.53524554758107</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-20828499.91459402</v>
+      </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
@@ -933,28 +933,28 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="P3" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.333333333333336</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="T3" t="n">
-        <v>4.333333333333336</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>2.083333333333334</v>
+        <v>6.75</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5833333333333335</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>0.5366666666666666</v>
@@ -963,16 +963,16 @@
         <v>0.8383333333333336</v>
       </c>
       <c r="Y3" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="AA3" t="n">
         <v>3.166666666666666</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>1.416666666666666</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.666666666666667</v>
       </c>
       <c r="AC3" t="n">
         <v>0.3999999999999999</v>
@@ -981,16 +981,16 @@
         <v>-0.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.083333333333334</v>
       </c>
       <c r="AF3" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>10</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
@@ -998,51 +998,51 @@
         <v>78.76801346801348</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.85696969696968</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-1.560371935855681</v>
-      </c>
+        <v>77.85375573921029</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>0.8600168350168076</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-7.186501377410465</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-51413177.2268136</v>
+      </c>
       <c r="AP3" t="n">
-        <v>-3.155808080808079</v>
+        <v>-4.217263544536266</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>-6.906925140326337</v>
-      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>4.734041241776936</v>
+        <v>4.662498772541994</v>
       </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>-1.347658402203856</v>
+      </c>
       <c r="AV3" t="n">
-        <v>-51974579.12457912</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-29818279.90304367</v>
-      </c>
+        <v>-3.051790633608814</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-7.229292929292924</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>-0.6003593821898774</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-4.165824915824913</v>
-      </c>
+        <v>-1.691146771888398</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.020018365472879</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.6495899142606152</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-1.368686868686869</v>
+        <v>-6.978295722220025</v>
       </c>
       <c r="BD3" t="n">
-        <v>-3.783660279230858</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>-3.821670648389343</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-30582204.89040975</v>
+      </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
@@ -1100,25 +1100,25 @@
         <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>-5</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
         <v>-0.8949999999999998</v>
@@ -1127,16 +1127,16 @@
         <v>1.085</v>
       </c>
       <c r="Y4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AA4" t="n">
         <v>-4.5</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>-3.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
       </c>
       <c r="AC4" t="n">
         <v>-1.5</v>
@@ -1145,16 +1145,16 @@
         <v>1.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
         <v>-1</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
@@ -1164,49 +1164,49 @@
       <c r="AL4" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AM4" t="n">
-        <v>-1.85137343987515</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>0.9303030303030084</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>-0.02499999999999147</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-2840227.272727277</v>
+      </c>
       <c r="AP4" t="n">
-        <v>0.262626262626263</v>
+        <v>-1.015909090909076</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>0.8422794147322605</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-3.644003838928569</v>
+        <v>-3.412103922423285</v>
       </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>-0.2500000000000004</v>
+      </c>
       <c r="AV4" t="n">
-        <v>-2567373.737373738</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>590628.4114840962</v>
-      </c>
+        <v>0.4215909090909093</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-0.0929292929292842</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>-0.05880993807812152</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-0.9282828282828177</v>
-      </c>
+        <v>-1.758528781459191</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.8818181818181756</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.0591532846929772</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>-0.2494949494949499</v>
+        <v>0.5584070336754223</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.319430534100235</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
+        <v>1.213244601807162</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-373016.4704373358</v>
+      </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
@@ -1261,28 +1261,28 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>-0.5</v>
       </c>
       <c r="U5" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="V5" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
         <v>0.9299999999999998</v>
@@ -1291,16 +1291,16 @@
         <v>-1.285</v>
       </c>
       <c r="Y5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1</v>
       </c>
       <c r="AC5" t="n">
         <v>2</v>
@@ -1309,16 +1309,16 @@
         <v>-2.5</v>
       </c>
       <c r="AE5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-1.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
@@ -1328,49 +1328,49 @@
       <c r="AL5" t="n">
         <v>76.5</v>
       </c>
-      <c r="AM5" t="n">
-        <v>3.932435117217729</v>
-      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>0.4767676767676505</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>-0.5788961038960849</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-6566688.311688308</v>
+      </c>
       <c r="AP5" t="n">
-        <v>1.720202020202024</v>
+        <v>-1.115584415584408</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>-0.23545468179951</v>
-      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-2.211052703177643</v>
+        <v>-2.344286824578319</v>
       </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>0.03051948051948061</v>
+      </c>
       <c r="AV5" t="n">
-        <v>-7140101.010101002</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-5597251.616995063</v>
-      </c>
+        <v>1.751623376623378</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-0.686868686868678</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>0.003607611248276132</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-1.246464646464659</v>
-      </c>
+        <v>3.723382610620007</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.532467532467507</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.01246849118435223</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>-0.002020202020202255</v>
+        <v>-0.1528413069773364</v>
       </c>
       <c r="BD5" t="n">
-        <v>-2.078770594755241</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
+        <v>-1.910130074757177</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-5104078.211303459</v>
+      </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
@@ -1425,28 +1425,28 @@
         <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>18.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-18.33333333333334</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="V6" t="n">
-        <v>-11.33333333333333</v>
+        <v>-21.66666666666667</v>
       </c>
       <c r="W6" t="n">
         <v>2.831666666666667</v>
@@ -1455,16 +1455,16 @@
         <v>-2.891666666666667</v>
       </c>
       <c r="Y6" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="AA6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>2.333333333333334</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
@@ -1473,16 +1473,16 @@
         <v>-3</v>
       </c>
       <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>-3.166666666666667</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-21.66666666666667</v>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1492,49 +1492,49 @@
       <c r="AL6" t="n">
         <v>84.92727272727274</v>
       </c>
-      <c r="AM6" t="n">
-        <v>0.6395235638114904</v>
-      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>0.06126543209876445</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>6.823302469135797</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>45962553.04783951</v>
+      </c>
       <c r="AP6" t="n">
-        <v>-1.92546296296296</v>
+        <v>6.690779320987659</v>
       </c>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>9.422332167316682</v>
-      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>-1.619370730748443</v>
+        <v>-1.181552868356249</v>
       </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>0.7966820987654317</v>
+      </c>
       <c r="AV6" t="n">
-        <v>46122029.32098766</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>29354422.66539789</v>
-      </c>
+        <v>-1.871527777777775</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>6.808487654320999</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="n">
-        <v>0.4937788767819729</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.745061728395044</v>
-      </c>
+        <v>0.359199190042844</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.1163194444444287</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4806652884439262</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>0.7885802469135799</v>
+        <v>9.138795685738401</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.836109123075062</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
+        <v>5.931281691304903</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>29274081.18949334</v>
+      </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
@@ -1542,7 +1542,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1555,10 +1555,10 @@
         <v>146</v>
       </c>
       <c r="E7" t="n">
-        <v>253</v>
+        <v>392</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>312</v>
       </c>
       <c r="G7" t="n">
         <v>48</v>
@@ -1580,125 +1580,125 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>311</v>
+        <v>145</v>
       </c>
       <c r="M7" t="n">
-        <v>271</v>
+        <v>403</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-14.75</v>
+        <v>-0.25</v>
       </c>
       <c r="T7" t="n">
-        <v>14.75</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.0349999999999997</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.4700000000000002</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB7" t="n">
         <v>-2.75</v>
       </c>
-      <c r="W7" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.1925</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AF7" t="n">
         <v>-1</v>
       </c>
-      <c r="AC7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-2</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
-        <v>77.02146464646464</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AL7" t="n">
-        <v>75.80000000000001</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.850529250983385</v>
-      </c>
+        <v>80.13415404040404</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>1.802918069584734</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>-0.03749999999999432</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-112321.4285714291</v>
+      </c>
       <c r="AP7" t="n">
-        <v>1.552300785634117</v>
+        <v>-0.2910714285714278</v>
       </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>-0.003630135120403111</v>
-      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>8.059273693077529</v>
+        <v>2.362852243863756</v>
       </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>0.1089285714285715</v>
+      </c>
       <c r="AV7" t="n">
-        <v>1861301.907968573</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-1243673.984887624</v>
-      </c>
+        <v>0.9857142857142875</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>1.206846240179587</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>-0.0007441557858842707</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.9500561167227914</v>
-      </c>
+        <v>0.9000830395087078</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.742857142857105</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.1161873589842288</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>0.2061728395061724</v>
+        <v>0.9510967786844304</v>
       </c>
       <c r="BD7" t="n">
-        <v>-3.187342346168066</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
+        <v>0.3619543532862792</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-238945.7190112025</v>
+      </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
@@ -1706,7 +1706,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1719,10 +1719,10 @@
         <v>146</v>
       </c>
       <c r="E8" t="n">
-        <v>624</v>
+        <v>253</v>
       </c>
       <c r="F8" t="n">
-        <v>419</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -1744,125 +1744,125 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>389</v>
+        <v>311</v>
       </c>
       <c r="M8" t="n">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.5</v>
       </c>
-      <c r="T8" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.2999999999999998</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.3799999999999999</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-2.800000000000001</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.7000000000000002</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.6000000000000001</v>
-      </c>
       <c r="AD8" t="n">
-        <v>-0.8999999999999999</v>
+        <v>-2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-2.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.800000000000001</v>
+        <v>-2</v>
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
-        <v>73.29545454545455</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AL8" t="n">
-        <v>72.99111111111111</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.187496107898919</v>
-      </c>
+        <v>75.80000000000001</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>5.630505050505064</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>1.214520202020211</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1834589.646464648</v>
+      </c>
       <c r="AP8" t="n">
-        <v>0.9371950271950311</v>
+        <v>-1.000631313131322</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
-        <v>2.316979761500221</v>
-      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>2.569776904680964</v>
+        <v>8.367477054386455</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>0.213762626262626</v>
+      </c>
       <c r="AV8" t="n">
-        <v>14679362.08236209</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8456518.499563098</v>
-      </c>
+        <v>1.680429292929293</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>4.997785547785554</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>0.3882900432900431</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.616324786324782</v>
-      </c>
+        <v>1.436444162587492</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.566919191919197</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.04747189620826719</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>0.5293939393939393</v>
+        <v>-0.2379628116184165</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.443425715375852</v>
-      </c>
-      <c r="BE8" t="inlineStr"/>
+        <v>-3.104791532682242</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1201358.571683187</v>
+      </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
@@ -1870,7 +1870,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1883,10 +1883,10 @@
         <v>146</v>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>624</v>
       </c>
       <c r="F9" t="n">
-        <v>312</v>
+        <v>419</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1908,125 +1908,125 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>145</v>
+        <v>389</v>
       </c>
       <c r="M9" t="n">
-        <v>403</v>
+        <v>77</v>
       </c>
       <c r="N9" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-8</v>
+        <v>-2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.75</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0349999999999997</v>
+        <v>1.316</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4700000000000002</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2.75</v>
+        <v>-2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.25</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.75</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.75</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.75</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.25</v>
+        <v>3.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>-6</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="n">
-        <v>81.76666666666667</v>
+        <v>73.29545454545455</v>
       </c>
       <c r="AL9" t="n">
-        <v>80.13415404040404</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.9373982822216078</v>
-      </c>
+        <v>72.99111111111111</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>3.584444444444415</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+        <v>4.902169421487613</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>14692283.05785124</v>
+      </c>
       <c r="AP9" t="n">
-        <v>0.8288888888888906</v>
+        <v>4.699896694214871</v>
       </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>0.7075875852733304</v>
-      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>2.056395486944524</v>
+        <v>2.517704458265484</v>
       </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>0.5102272727272728</v>
+      </c>
       <c r="AV9" t="n">
-        <v>19666.66666666605</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-534417.4824704174</v>
-      </c>
+        <v>0.7660123966942081</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>-0.1055555555555543</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>0.1306318391952392</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-0.2422222222222388</v>
-      </c>
+        <v>1.409744653790366</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5.375206611570235</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.4238095238095236</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>0.118888888888889</v>
+        <v>3.202640962511481</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.007013003037698695</v>
-      </c>
-      <c r="BE9" t="inlineStr"/>
+        <v>2.96223784474266</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10053627.24598238</v>
+      </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
@@ -2080,25 +2080,25 @@
       <c r="N10" t="n">
         <v>-3</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>-3</v>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-4</v>
+        <v>0.25</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.25</v>
+        <v>4.25</v>
       </c>
       <c r="V10" t="n">
-        <v>-4</v>
+        <v>-9.5</v>
       </c>
       <c r="W10" t="n">
         <v>-0.1925000000000001</v>
@@ -2107,16 +2107,16 @@
         <v>-1.3675</v>
       </c>
       <c r="Y10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
         <v>-3.25</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
         <v>1.75</v>
@@ -2125,16 +2125,16 @@
         <v>-1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="AF10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-9.5</v>
       </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
@@ -2142,49 +2142,49 @@
       <c r="AL10" t="n">
         <v>78.65909090909091</v>
       </c>
-      <c r="AM10" t="n">
-        <v>1.856644212032641</v>
-      </c>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>-0.7672727272727116</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>-12.20606060606062</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-45110909.09090909</v>
+      </c>
       <c r="AP10" t="n">
-        <v>0.6181818181818137</v>
+        <v>-11.28787878787877</v>
       </c>
       <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>-10.55549400194862</v>
-      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>-0.2009810010960678</v>
+        <v>-0.06185875316307943</v>
       </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>-1.65050505050505</v>
+      </c>
       <c r="AV10" t="n">
-        <v>-44092090.90909091</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-32198919.6352454</v>
-      </c>
+        <v>0.4595959595959549</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>-11.91727272727273</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="n">
-        <v>-0.8132648276701988</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-11.20681818181816</v>
-      </c>
+        <v>1.938006096158269</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.6909090909090878</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.8513400046008743</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>-1.621818181818182</v>
+        <v>-10.60447435012652</v>
       </c>
       <c r="BD10" t="n">
-        <v>-11.09582914687613</v>
-      </c>
-      <c r="BE10" t="inlineStr"/>
+        <v>-11.21757821486082</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-32647976.76558546</v>
+      </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
@@ -2239,28 +2239,28 @@
         <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="W11" t="n">
         <v>0.8125</v>
@@ -2269,16 +2269,16 @@
         <v>-0.08499999999999996</v>
       </c>
       <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
         <v>-0.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.5</v>
       </c>
       <c r="AC11" t="n">
         <v>-0.3999999999999999</v>
@@ -2287,68 +2287,68 @@
         <v>0.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="n">
-        <v>77.9919696969697</v>
+        <v>77.97987603305785</v>
       </c>
       <c r="AL11" t="n">
         <v>74.54545454545453</v>
       </c>
-      <c r="AM11" t="n">
-        <v>-3.82273049426183</v>
-      </c>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>0.772474747474746</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
+        <v>2.722746950019683</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>17019983.60225633</v>
+      </c>
       <c r="AP11" t="n">
-        <v>-2.187542087542088</v>
+        <v>5.466745375836283</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
-        <v>0.3442508678921712</v>
-      </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>2.684438527277422</v>
+        <v>2.544944017851492</v>
       </c>
       <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>0.6762691853600942</v>
+      </c>
       <c r="AV11" t="n">
-        <v>16866637.20538721</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>12046064.33408343</v>
-      </c>
+        <v>-2.333989243080151</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>2.726262626262638</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="n">
-        <v>0.5558858743321657</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.328535353535358</v>
-      </c>
+        <v>-3.654831907610326</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.7954742227468898</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.5276486675638035</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>0.6883838383838383</v>
+        <v>0.02235611336402599</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.367332947671812</v>
-      </c>
-      <c r="BE11" t="inlineStr"/>
+        <v>5.024274162893079</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>10984469.04336654</v>
+      </c>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
@@ -2403,28 +2403,28 @@
         <v>9</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5.666666666666664</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.666666666666664</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.333333333333333</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.333333333333333</v>
+        <v>-7.333333333333333</v>
       </c>
       <c r="W12" t="n">
         <v>-0.3266666666666667</v>
@@ -2433,16 +2433,16 @@
         <v>-1.066666666666667</v>
       </c>
       <c r="Y12" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="AA12" t="n">
         <v>6.666666666666668</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4</v>
       </c>
       <c r="AC12" t="n">
         <v>-2</v>
@@ -2451,16 +2451,16 @@
         <v>2</v>
       </c>
       <c r="AE12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AG12" t="n">
         <v>-2.333333333333333</v>
       </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.666666666666666</v>
-      </c>
       <c r="AH12" t="n">
-        <v>-7.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
@@ -2470,49 +2470,49 @@
       <c r="AL12" t="n">
         <v>69</v>
       </c>
-      <c r="AM12" t="n">
-        <v>2.537110809082559</v>
-      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="n">
-        <v>2.31852617079889</v>
-      </c>
-      <c r="AO12" t="inlineStr"/>
+        <v>4.648877665544319</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>6137873.176206509</v>
+      </c>
       <c r="AP12" t="n">
-        <v>-1.11623048668503</v>
+        <v>4.746520763187448</v>
       </c>
       <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="n">
-        <v>7.334945108426126</v>
-      </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>1.362754095319872</v>
+        <v>0.8657106619825754</v>
       </c>
       <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>0.1550505050505051</v>
+      </c>
       <c r="AV12" t="n">
-        <v>6015646.235078054</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>3510151.26442937</v>
-      </c>
+        <v>-1.061503928170595</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>4.410445362718065</v>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="n">
-        <v>0.06099221985444903</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.632380624426091</v>
-      </c>
+        <v>2.571972157433972</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.392087542087609</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.04603727455894635</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="n">
-        <v>0.1529958677685948</v>
+        <v>7.331146766698879</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.212224376930266</v>
-      </c>
-      <c r="BE12" t="inlineStr"/>
+        <v>3.016572387689507</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3577584.255148304</v>
+      </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>45518.65625</v>
       </c>
       <c r="C13" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D13" t="n">
         <v>146</v>
@@ -2561,7 +2561,7 @@
         <v>428</v>
       </c>
       <c r="M13" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -2665,25 +2665,25 @@
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>21.5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>-21.5</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
         <v>8</v>
@@ -2695,16 +2695,16 @@
         <v>0.665</v>
       </c>
       <c r="Y14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>-2.5</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>7.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-1</v>
       </c>
       <c r="AC14" t="n">
         <v>-2</v>
@@ -2713,16 +2713,16 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>8</v>
       </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
@@ -2732,49 +2732,49 @@
       <c r="AL14" t="n">
         <v>69.5409090909091</v>
       </c>
-      <c r="AM14" t="n">
-        <v>-0.083286126447355</v>
-      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="n">
-        <v>-3.375252525252478</v>
-      </c>
-      <c r="AO14" t="inlineStr"/>
+        <v>2.123376623376615</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1776341.991341992</v>
+      </c>
       <c r="AP14" t="n">
-        <v>-2.49267676767677</v>
+        <v>4.493073593073603</v>
       </c>
       <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="n">
-        <v>3.658565308168363</v>
-      </c>
+      <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
-        <v>-4.083728128932705</v>
+        <v>-4.192364047068082</v>
       </c>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>0.09220779220779241</v>
+      </c>
       <c r="AV14" t="n">
-        <v>1897077.02020202</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1286850.884526516</v>
-      </c>
+        <v>-2.962770562770565</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="n">
-        <v>2.596212121212119</v>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="n">
-        <v>0.005927050771999509</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.459595959595973</v>
-      </c>
+        <v>0.0640253202730392</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-3.160173160173173</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.01481295416717421</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>0.09393939393939421</v>
+        <v>4.043052003410054</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.174513595695927</v>
-      </c>
-      <c r="BE14" t="inlineStr"/>
+        <v>4.433221114532756</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1651013.664523781</v>
+      </c>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>45517.66666666666</v>
       </c>
       <c r="C15" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D15" t="n">
         <v>146</v>
@@ -2823,20 +2823,12 @@
         <v>110</v>
       </c>
       <c r="M15" t="n">
-        <v>430</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2888,23 +2880,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C16" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D16" t="n">
         <v>146</v>
       </c>
       <c r="E16" t="n">
-        <v>245</v>
+        <v>781</v>
       </c>
       <c r="F16" t="n">
-        <v>441</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -2926,18 +2918,18 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="M16" t="n">
-        <v>430</v>
+        <v>168</v>
       </c>
       <c r="N16" t="n">
         <v>-2</v>
       </c>
-      <c r="O16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
@@ -2960,10 +2952,10 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="n">
-        <v>69.13636363636363</v>
-      </c>
-      <c r="AL16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
@@ -2990,23 +2982,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C17" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D17" t="n">
         <v>146</v>
       </c>
       <c r="E17" t="n">
-        <v>566</v>
+        <v>245</v>
       </c>
       <c r="F17" t="n">
-        <v>540</v>
+        <v>441</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -3028,23 +3020,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="M17" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N17" t="n">
         <v>-2</v>
       </c>
-      <c r="O17" t="n">
-        <v>-2</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>-1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3066,7 +3054,9 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AK17" t="n">
+        <v>69.13636363636363</v>
+      </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
@@ -3094,23 +3084,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C18" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D18" t="n">
         <v>146</v>
       </c>
       <c r="E18" t="n">
-        <v>740</v>
+        <v>436</v>
       </c>
       <c r="F18" t="n">
-        <v>412</v>
+        <v>734</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -3132,124 +3122,56 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>331</v>
+        <v>435</v>
       </c>
       <c r="M18" t="n">
-        <v>236</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-1</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="n">
-        <v>-21</v>
-      </c>
-      <c r="T18" t="n">
-        <v>21</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>9</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="n">
-        <v>74</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>69</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.018441460376287</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.117245370370341</v>
-      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="n">
-        <v>4.656327160493827</v>
-      </c>
+      <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="n">
-        <v>0.3003679171335136</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.5588051963200087</v>
-      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="n">
-        <v>-1287210.648148148</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>-109708.5345255611</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.2523148148148096</v>
-      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-5.889969135802474</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>-0.4068603831073148</v>
-      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
         <v>0</v>
@@ -3258,23 +3180,23 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C19" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D19" t="n">
         <v>146</v>
       </c>
       <c r="E19" t="n">
-        <v>729</v>
+        <v>399</v>
       </c>
       <c r="F19" t="n">
-        <v>699</v>
+        <v>542</v>
       </c>
       <c r="G19" t="n">
         <v>48</v>
@@ -3296,17 +3218,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M19" t="n">
-        <v>430</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
@@ -3358,23 +3276,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C20" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D20" t="n">
         <v>146</v>
       </c>
       <c r="E20" t="n">
-        <v>781</v>
+        <v>729</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>699</v>
       </c>
       <c r="G20" t="n">
         <v>48</v>
@@ -3396,18 +3314,18 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M20" t="n">
-        <v>168</v>
+        <v>434</v>
       </c>
       <c r="N20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
@@ -3431,9 +3349,7 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
@@ -3460,23 +3376,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C21" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D21" t="n">
         <v>146</v>
       </c>
       <c r="E21" t="n">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="F21" t="n">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="G21" t="n">
         <v>48</v>
@@ -3498,18 +3414,18 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="M21" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
@@ -3532,7 +3448,9 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AK21" t="n">
+        <v>69.2</v>
+      </c>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
@@ -3560,23 +3478,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D22" t="n">
         <v>146</v>
       </c>
       <c r="E22" t="n">
-        <v>233</v>
+        <v>387</v>
       </c>
       <c r="F22" t="n">
-        <v>426</v>
+        <v>501</v>
       </c>
       <c r="G22" t="n">
         <v>48</v>
@@ -3598,19 +3516,23 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="M22" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1</v>
+      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3633,7 +3555,7 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="n">
-        <v>69.2</v>
+        <v>69.64141414141415</v>
       </c>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
@@ -3662,23 +3584,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C23" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D23" t="n">
         <v>146</v>
       </c>
       <c r="E23" t="n">
-        <v>399</v>
+        <v>566</v>
       </c>
       <c r="F23" t="n">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -3700,10 +3622,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M23" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -3758,23 +3680,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C24" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D24" t="n">
         <v>146</v>
       </c>
       <c r="E24" t="n">
-        <v>555</v>
+        <v>338</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="G24" t="n">
         <v>48</v>
@@ -3796,23 +3718,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>431</v>
+        <v>73</v>
       </c>
       <c r="M24" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -3834,7 +3752,9 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
+      <c r="AK24" t="n">
+        <v>70.70833333333333</v>
+      </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
@@ -3862,23 +3782,23 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C25" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D25" t="n">
         <v>146</v>
       </c>
       <c r="E25" t="n">
-        <v>436</v>
+        <v>555</v>
       </c>
       <c r="F25" t="n">
-        <v>734</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -3900,17 +3820,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M25" t="n">
-        <v>430</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
@@ -3962,23 +3878,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C26" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
         <v>146</v>
       </c>
       <c r="E26" t="n">
-        <v>387</v>
+        <v>278</v>
       </c>
       <c r="F26" t="n">
-        <v>501</v>
+        <v>376</v>
       </c>
       <c r="G26" t="n">
         <v>48</v>
@@ -4000,23 +3916,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>347</v>
+        <v>435</v>
       </c>
       <c r="M26" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4038,9 +3950,7 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
@@ -4068,23 +3978,23 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C27" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D27" t="n">
         <v>146</v>
       </c>
       <c r="E27" t="n">
-        <v>182</v>
+        <v>540</v>
       </c>
       <c r="F27" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -4106,23 +4016,15 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M27" t="n">
-        <v>430</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4172,23 +4074,23 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C28" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D28" t="n">
         <v>146</v>
       </c>
       <c r="E28" t="n">
-        <v>540</v>
+        <v>182</v>
       </c>
       <c r="F28" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -4210,13 +4112,17 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M28" t="n">
-        <v>430</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+        <v>434</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
@@ -4268,23 +4174,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C29" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D29" t="n">
         <v>146</v>
       </c>
       <c r="E29" t="n">
-        <v>338</v>
+        <v>740</v>
       </c>
       <c r="F29" t="n">
-        <v>125</v>
+        <v>412</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -4306,63 +4212,125 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>73</v>
+        <v>331</v>
       </c>
       <c r="M29" t="n">
-        <v>430</v>
+        <v>236</v>
       </c>
       <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>1</v>
       </c>
-      <c r="O29" t="n">
+      <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-21</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2</v>
+      </c>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="n">
-        <v>70.70833333333333</v>
-      </c>
-      <c r="AL29" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>69</v>
+      </c>
       <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
+      <c r="AN29" t="n">
+        <v>0.3376984126984013</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-1281253.306878306</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-5.914153439153438</v>
+      </c>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
+      <c r="AS29" t="n">
+        <v>0.2953982603720817</v>
+      </c>
       <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.621296296296293</v>
+      </c>
       <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
+      <c r="AX29" t="n">
+        <v>1.216519796764572</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.906944444444434</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
       <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="inlineStr"/>
+      <c r="BC29" t="n">
+        <v>0.4217652273900256</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>-0.5411850373547225</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>-130365.5393059938</v>
+      </c>
       <c r="BF29" t="n">
         <v>0</v>
       </c>
@@ -4370,23 +4338,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C30" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D30" t="n">
         <v>146</v>
       </c>
       <c r="E30" t="n">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="F30" t="n">
-        <v>194</v>
+        <v>368</v>
       </c>
       <c r="G30" t="n">
         <v>48</v>
@@ -4408,124 +4376,56 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="M30" t="n">
-        <v>209</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="n">
-        <v>21</v>
-      </c>
-      <c r="T30" t="n">
-        <v>-21</v>
-      </c>
-      <c r="U30" t="n">
-        <v>4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>-6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X30" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>-24</v>
-      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>70.18181818181819</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.481839318662072</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>-1.653888888888872</v>
-      </c>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="n">
-        <v>-0.617986111111108</v>
-      </c>
+      <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="n">
-        <v>-2.218100666103766</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.2448807569279836</v>
-      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="n">
-        <v>-2184951.388888889</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>-1374683.396464646</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>-2.831736111111098</v>
-      </c>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>-2.584305555555559</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>-2.872966736136249</v>
-      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
       <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="n">
         <v>0</v>
@@ -4534,23 +4434,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C31" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D31" t="n">
         <v>146</v>
       </c>
       <c r="E31" t="n">
-        <v>684</v>
+        <v>621</v>
       </c>
       <c r="F31" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
         <v>48</v>
@@ -4572,10 +4472,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M31" t="n">
-        <v>333</v>
+        <v>434</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -4603,9 +4503,7 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
@@ -4632,23 +4530,23 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C32" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D32" t="n">
         <v>146</v>
       </c>
       <c r="E32" t="n">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F32" t="n">
-        <v>368</v>
+        <v>488</v>
       </c>
       <c r="G32" t="n">
         <v>48</v>
@@ -4670,10 +4568,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M32" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -4728,23 +4626,23 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C33" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D33" t="n">
         <v>146</v>
       </c>
       <c r="E33" t="n">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="F33" t="n">
-        <v>687</v>
+        <v>473</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -4766,10 +4664,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M33" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -4824,23 +4722,23 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D34" t="n">
         <v>146</v>
       </c>
       <c r="E34" t="n">
-        <v>764</v>
+        <v>309</v>
       </c>
       <c r="F34" t="n">
-        <v>790</v>
+        <v>687</v>
       </c>
       <c r="G34" t="n">
         <v>48</v>
@@ -4862,10 +4760,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>346</v>
+        <v>435</v>
       </c>
       <c r="M34" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -4892,9 +4790,7 @@
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="n">
-        <v>69.33522727272728</v>
-      </c>
+      <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
@@ -4922,23 +4818,23 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C35" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D35" t="n">
         <v>146</v>
       </c>
       <c r="E35" t="n">
-        <v>307</v>
+        <v>764</v>
       </c>
       <c r="F35" t="n">
-        <v>50</v>
+        <v>790</v>
       </c>
       <c r="G35" t="n">
         <v>48</v>
@@ -4960,10 +4856,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>431</v>
+        <v>346</v>
       </c>
       <c r="M35" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -4990,7 +4886,9 @@
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
+      <c r="AK35" t="n">
+        <v>69.33522727272728</v>
+      </c>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
@@ -5018,23 +4916,23 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C36" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D36" t="n">
         <v>146</v>
       </c>
       <c r="E36" t="n">
-        <v>621</v>
+        <v>273</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -5056,57 +4954,125 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="M36" t="n">
-        <v>430</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>7</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-24</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
+      <c r="AK36" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>70.18181818181819</v>
+      </c>
       <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
+      <c r="AN36" t="n">
+        <v>-2.816666666666649</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>-2234641.203703703</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>-2.82534722222222</v>
+      </c>
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
+      <c r="AS36" t="n">
+        <v>-0.2023692810457476</v>
+      </c>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>-0.5010416666666657</v>
+      </c>
       <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
+      <c r="AX36" t="n">
+        <v>1.301905073233439</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>-1.420370370370335</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
+      <c r="BC36" t="n">
+        <v>-2.202103660443441</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>-2.49301163447835</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>-1269591.292981506</v>
+      </c>
       <c r="BF36" t="n">
         <v>0</v>
       </c>
@@ -5114,23 +5080,23 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C37" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D37" t="n">
         <v>146</v>
       </c>
       <c r="E37" t="n">
-        <v>228</v>
+        <v>684</v>
       </c>
       <c r="F37" t="n">
-        <v>488</v>
+        <v>139</v>
       </c>
       <c r="G37" t="n">
         <v>48</v>
@@ -5152,17 +5118,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M37" t="n">
-        <v>430</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
@@ -5187,7 +5149,9 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
+      <c r="AL37" t="n">
+        <v>72.22962962962963</v>
+      </c>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
@@ -5214,7 +5178,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -5227,10 +5191,10 @@
         <v>146</v>
       </c>
       <c r="E38" t="n">
-        <v>590</v>
+        <v>504</v>
       </c>
       <c r="F38" t="n">
-        <v>600</v>
+        <v>353</v>
       </c>
       <c r="G38" t="n">
         <v>48</v>
@@ -5252,14 +5216,18 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M38" t="n">
-        <v>209</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
         <v>0</v>
@@ -5284,7 +5252,7 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>71.77777777777777</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
@@ -5312,23 +5280,23 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C39" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D39" t="n">
         <v>146</v>
       </c>
       <c r="E39" t="n">
-        <v>528</v>
+        <v>756</v>
       </c>
       <c r="F39" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G39" t="n">
         <v>48</v>
@@ -5350,18 +5318,18 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="M39" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
         <v>-1</v>
       </c>
-      <c r="O39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
         <v>0</v>
@@ -5384,9 +5352,7 @@
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
@@ -5414,23 +5380,23 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C40" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D40" t="n">
         <v>146</v>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="F40" t="n">
-        <v>353</v>
+        <v>191</v>
       </c>
       <c r="G40" t="n">
         <v>48</v>
@@ -5452,17 +5418,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="M40" t="n">
-        <v>175</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
@@ -5486,10 +5448,10 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="n">
-        <v>67.40000000000001</v>
-      </c>
+      <c r="AK40" t="n">
+        <v>71.47727272727272</v>
+      </c>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
@@ -5516,23 +5478,23 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C41" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D41" t="n">
         <v>146</v>
       </c>
       <c r="E41" t="n">
-        <v>756</v>
+        <v>590</v>
       </c>
       <c r="F41" t="n">
-        <v>181</v>
+        <v>600</v>
       </c>
       <c r="G41" t="n">
         <v>48</v>
@@ -5554,17 +5516,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M41" t="n">
-        <v>430</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-2</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
@@ -5589,7 +5547,9 @@
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
+      <c r="AL41" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
@@ -5616,23 +5576,23 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C42" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D42" t="n">
         <v>146</v>
       </c>
       <c r="E42" t="n">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="F42" t="n">
-        <v>759</v>
+        <v>50</v>
       </c>
       <c r="G42" t="n">
         <v>48</v>
@@ -5654,17 +5614,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M42" t="n">
-        <v>430</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
@@ -5716,23 +5672,23 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C43" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D43" t="n">
         <v>146</v>
       </c>
       <c r="E43" t="n">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="F43" t="n">
-        <v>473</v>
+        <v>759</v>
       </c>
       <c r="G43" t="n">
         <v>48</v>
@@ -5754,10 +5710,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M43" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -5812,7 +5768,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -5825,10 +5781,10 @@
         <v>146</v>
       </c>
       <c r="E44" t="n">
-        <v>217</v>
+        <v>483</v>
       </c>
       <c r="F44" t="n">
-        <v>74</v>
+        <v>537</v>
       </c>
       <c r="G44" t="n">
         <v>48</v>
@@ -5850,10 +5806,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M44" t="n">
-        <v>278</v>
+        <v>221</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -5882,7 +5838,7 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>76</v>
+        <v>71.2</v>
       </c>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
@@ -5910,23 +5866,23 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
       <c r="C45" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D45" t="n">
         <v>146</v>
       </c>
       <c r="E45" t="n">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="F45" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="G45" t="n">
         <v>48</v>
@@ -5948,17 +5904,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M45" t="n">
-        <v>430</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
@@ -5983,7 +5935,9 @@
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
+      <c r="AL45" t="n">
+        <v>76</v>
+      </c>
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
@@ -6010,23 +5964,23 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
       <c r="C46" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D46" t="n">
         <v>146</v>
       </c>
       <c r="E46" t="n">
-        <v>483</v>
+        <v>244</v>
       </c>
       <c r="F46" t="n">
-        <v>537</v>
+        <v>152</v>
       </c>
       <c r="G46" t="n">
         <v>48</v>
@@ -6048,10 +6002,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M46" t="n">
-        <v>221</v>
+        <v>434</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -6079,9 +6033,7 @@
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
@@ -6155,28 +6107,28 @@
         <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="P47" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="V47" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
         <v>0.1174999999999999</v>
@@ -6185,16 +6137,16 @@
         <v>0.5950000000000002</v>
       </c>
       <c r="Y47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA47" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
         <v>-2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.5</v>
       </c>
       <c r="AC47" t="n">
         <v>-1.25</v>
@@ -6203,16 +6155,16 @@
         <v>1</v>
       </c>
       <c r="AE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG47" t="n">
         <v>-1</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>6.5</v>
       </c>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
@@ -6222,49 +6174,49 @@
       <c r="AL47" t="n">
         <v>77.36540404040404</v>
       </c>
-      <c r="AM47" t="n">
-        <v>-0.3707263230281157</v>
-      </c>
+      <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="n">
-        <v>2.906565656565647</v>
-      </c>
-      <c r="AO47" t="inlineStr"/>
+        <v>-5.467217630854009</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>-42477277.31864096</v>
+      </c>
       <c r="AP47" t="n">
-        <v>-1.729208754208756</v>
+        <v>-3.063360881542692</v>
       </c>
       <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="n">
-        <v>-4.997674767096129</v>
-      </c>
+      <c r="AR47" t="inlineStr"/>
       <c r="AS47" t="n">
-        <v>5.760937278951985</v>
+        <v>5.571349283515019</v>
       </c>
       <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
+      <c r="AU47" t="n">
+        <v>-0.8917355371900828</v>
+      </c>
       <c r="AV47" t="n">
-        <v>-43387504.2087542</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>-25716382.34990418</v>
-      </c>
+        <v>-1.708723599632687</v>
+      </c>
+      <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="n">
-        <v>-5.511616161616161</v>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="n">
-        <v>-0.4099647291942687</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>-3.101262626262624</v>
-      </c>
+        <v>-0.6278392923824185</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>2.907988980716226</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>-0.4772401918007592</v>
+      </c>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="n">
-        <v>-0.9106060606060611</v>
+        <v>-5.534005271769757</v>
       </c>
       <c r="BD47" t="n">
-        <v>-3.458909711227491</v>
-      </c>
-      <c r="BE47" t="inlineStr"/>
+        <v>-3.686012020091297</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>-27542234.39953895</v>
+      </c>
       <c r="BF47" t="n">
         <v>1</v>
       </c>

--- a/p6_deployment/data/england/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_tagged.xlsx
@@ -520,94 +520,94 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -620,97 +620,97 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -781,103 +781,103 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AB2" t="n">
         <v>-1.666666666666667</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="n">
+        <v>-0.7333333333333329</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V2" t="n">
-        <v>-7.666666666666666</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-0.7333333333333329</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
         <v>71.22727272727272</v>
       </c>
       <c r="AL2" t="n">
         <v>77.21818181818182</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
+      <c r="AM2" t="n">
         <v>-5.786111111111126</v>
       </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
+        <v>-0.6529583972743467</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-5.53524554758107</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-20828499.91459402</v>
+      </c>
+      <c r="AR2" t="n">
         <v>-29846130.95238096</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
+        <v>-0.2652031356801094</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.6529761904761904</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-2.036111111111097</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.610714285714284</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
         <v>-6.928968253968279</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>-0.6529583972743467</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>-0.6529761904761904</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.610714285714284</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>1.697725122744469</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-2.036111111111097</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.2652031356801094</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
         <v>-4.617364768874054</v>
       </c>
-      <c r="BD2" t="n">
-        <v>-5.53524554758107</v>
-      </c>
       <c r="BE2" t="n">
-        <v>-20828499.91459402</v>
+        <v>1.697725122744469</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -945,103 +945,103 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.416666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U3" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="Y3" t="n">
         <v>6.75</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
         <v>10</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0.5366666666666666</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AD3" t="n">
         <v>0.8383333333333336</v>
       </c>
-      <c r="Y3" t="n">
-        <v>-4.333333333333336</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.333333333333336</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.416666666666666</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AJ3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AE3" t="n">
-        <v>2.083333333333334</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.5833333333333335</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
         <v>78.76801346801348</v>
       </c>
       <c r="AL3" t="n">
         <v>77.85375573921029</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>-7.186501377410465</v>
-      </c>
+      <c r="AM3" t="n">
+        <v>-7.368484848484854</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>-51413177.2268136</v>
+        <v>4.663911373155372</v>
       </c>
       <c r="AP3" t="n">
-        <v>-4.217263544536266</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+        <v>-3.922110422454423</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-30861818.17709465</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-52528383.83838384</v>
+      </c>
       <c r="AS3" t="n">
-        <v>4.662498772541994</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>-1.347658402203856</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-3.051790633608814</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>-0.6644494615050729</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-1.394848484848485</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>0.7455555555555406</v>
+      </c>
       <c r="AX3" t="n">
-        <v>-1.691146771888398</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.020018365472879</v>
-      </c>
+        <v>-3.228484848484843</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-0.6495899142606152</v>
+        <v>-4.290404040404042</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="n">
-        <v>-6.978295722220025</v>
-      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-3.821670648389343</v>
+        <v>-7.193227926985998</v>
       </c>
       <c r="BE3" t="n">
-        <v>-30582204.89040975</v>
+        <v>-1.702080137329435</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
@@ -1109,103 +1109,103 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
+        <v>12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-5</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Z4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
         <v>-0.8949999999999998</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AD4" t="n">
         <v>1.085</v>
       </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AJ4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
         <v>77.95454545454545</v>
       </c>
       <c r="AL4" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>-0.02499999999999147</v>
-      </c>
+      <c r="AM4" t="n">
+        <v>0.08279220779220964</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-2840227.272727277</v>
+        <v>-3.019159858832978</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1.015909090909076</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+        <v>1.164141144634812</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-780645.2390500437</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-2588798.701298706</v>
+      </c>
       <c r="AS4" t="n">
-        <v>-3.412103922423285</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="n">
-        <v>-0.2500000000000004</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.4215909090909093</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>-0.07075274904011941</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.2418831168831173</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>0.7142857142857224</v>
+      </c>
       <c r="AX4" t="n">
-        <v>-1.758528781459191</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.8818181818181756</v>
-      </c>
+        <v>0.4009740259740262</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>-0.0591532846929772</v>
+        <v>-0.9415584415584277</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="n">
-        <v>0.5584070336754223</v>
-      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>1.213244601807162</v>
+        <v>0.4662913277439316</v>
       </c>
       <c r="BE4" t="n">
-        <v>-373016.4704373358</v>
+        <v>-1.6851765897053</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1273,103 +1273,103 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
         <v>12.5</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Z5" t="n">
         <v>1</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0.9299999999999998</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AD5" t="n">
         <v>-1.285</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-4</v>
       </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
         <v>2</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AJ5" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
         <v>77.62272727272727</v>
       </c>
       <c r="AL5" t="n">
         <v>76.5</v>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>-0.5788961038960849</v>
-      </c>
+      <c r="AM5" t="n">
+        <v>-1.028571428571425</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>-6566688.311688308</v>
+        <v>-2.482223040731469</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1.115584415584408</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+        <v>-1.855779584561105</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-4560738.276371153</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-7768311.688311685</v>
+      </c>
       <c r="AS5" t="n">
-        <v>-2.344286824578319</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>0.03051948051948061</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.751623376623378</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>0.03935195290237292</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.02467532467532463</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>0.7597402597402549</v>
+      </c>
       <c r="AX5" t="n">
-        <v>3.723382610620007</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.532467532467507</v>
-      </c>
+        <v>1.584415584415584</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>0.01246849118435223</v>
+        <v>-1.303896103896093</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
-        <v>-0.1528413069773364</v>
-      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>-1.910130074757177</v>
+        <v>-0.06373503947033043</v>
       </c>
       <c r="BE5" t="n">
-        <v>-5104078.211303459</v>
+        <v>3.697361368789938</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1437,103 +1437,103 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.666666666666667</v>
+        <v>-3.166666666666667</v>
       </c>
       <c r="U6" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="Y6" t="n">
         <v>22.66666666666667</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
         <v>-21.66666666666667</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.831666666666667</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AD6" t="n">
         <v>-2.891666666666667</v>
       </c>
-      <c r="Y6" t="n">
-        <v>18.33333333333334</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-18.33333333333334</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AI6" t="n">
         <v>3</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AJ6" t="n">
         <v>-3</v>
       </c>
-      <c r="AE6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-11.33333333333333</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-3.166666666666667</v>
-      </c>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
         <v>75.97205387205388</v>
       </c>
       <c r="AL6" t="n">
         <v>84.92727272727274</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
-        <v>6.823302469135797</v>
-      </c>
+      <c r="AM6" t="n">
+        <v>7.060763888888886</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>45962553.04783951</v>
+        <v>-1.492309818664296</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.690779320987659</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+        <v>5.901018756784993</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>28947364.23277445</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>47881727.43055556</v>
+      </c>
       <c r="AS6" t="n">
-        <v>-1.181552868356249</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="n">
-        <v>0.7966820987654317</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-1.871527777777775</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>0.4727499731950198</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.8263888888888886</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>0.07986111111111427</v>
+      </c>
       <c r="AX6" t="n">
-        <v>0.359199190042844</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.1163194444444287</v>
-      </c>
+        <v>-1.880208333333332</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>0.4806652884439262</v>
+        <v>6.868055555555557</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="n">
-        <v>9.138795685738401</v>
-      </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>5.931281691304903</v>
+        <v>9.096245041078632</v>
       </c>
       <c r="BE6" t="n">
-        <v>29274081.18949334</v>
+        <v>0.3440181335692181</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
@@ -1542,7 +1542,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1555,10 +1555,10 @@
         <v>146</v>
       </c>
       <c r="E7" t="n">
-        <v>392</v>
+        <v>253</v>
       </c>
       <c r="F7" t="n">
-        <v>312</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>48</v>
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>145</v>
+        <v>311</v>
       </c>
       <c r="M7" t="n">
-        <v>403</v>
+        <v>271</v>
       </c>
       <c r="N7" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>-2</v>
@@ -1601,103 +1601,103 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="X7" t="n">
         <v>-0.25</v>
       </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.0349999999999997</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.4700000000000002</v>
-      </c>
       <c r="Y7" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="AA7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>-2</v>
       </c>
-      <c r="AB7" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
-        <v>81.76666666666667</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AL7" t="n">
-        <v>80.13415404040404</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>-0.03749999999999432</v>
-      </c>
+        <v>75.80000000000001</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.171753246753255</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>-112321.4285714291</v>
+        <v>8.326102350265018</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.2910714285714278</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+        <v>-3.315135535049265</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1432068.723799587</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1775953.282828284</v>
+      </c>
       <c r="AS7" t="n">
-        <v>2.362852243863756</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>0.1089285714285715</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9857142857142875</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
+        <v>-0.06534905438147809</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.2233766233766232</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>1.620490620490642</v>
+      </c>
       <c r="AX7" t="n">
-        <v>0.9000830395087078</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.742857142857105</v>
-      </c>
+        <v>1.663816738816742</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>0.1161873589842288</v>
+        <v>-0.9375901875902031</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
-        <v>0.9510967786844304</v>
-      </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>0.3619543532862792</v>
+        <v>-0.2109521425847163</v>
       </c>
       <c r="BE7" t="n">
-        <v>-238945.7190112025</v>
+        <v>1.618717119284788</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1719,10 +1719,10 @@
         <v>146</v>
       </c>
       <c r="E8" t="n">
-        <v>253</v>
+        <v>624</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>419</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -1744,124 +1744,124 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>311</v>
+        <v>389</v>
       </c>
       <c r="M8" t="n">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-2</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.25</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.25</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.24</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1925</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>-14.75</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.75</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3.75</v>
+        <v>-2.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.25</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>1.316</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-2.75</v>
-      </c>
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
       <c r="AK8" t="n">
-        <v>77.02146464646464</v>
+        <v>73.29545454545455</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.80000000000001</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
-        <v>1.214520202020211</v>
-      </c>
+        <v>72.99111111111111</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>4.902169421487613</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>1834589.646464648</v>
+        <v>2.517704458265484</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.000631313131322</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
+        <v>2.96223784474266</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10053627.24598238</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14692283.05785124</v>
+      </c>
       <c r="AS8" t="n">
-        <v>8.367477054386455</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="n">
-        <v>0.213762626262626</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.680429292929293</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+        <v>0.4238095238095236</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.5102272727272728</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>5.375206611570235</v>
+      </c>
       <c r="AX8" t="n">
-        <v>1.436444162587492</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.566919191919197</v>
-      </c>
+        <v>0.7660123966942081</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>-0.04747189620826719</v>
+        <v>4.699896694214871</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="n">
-        <v>-0.2379628116184165</v>
-      </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>-3.104791532682242</v>
+        <v>3.202640962511481</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1201358.571683187</v>
+        <v>1.409744653790366</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1883,10 +1883,10 @@
         <v>146</v>
       </c>
       <c r="E9" t="n">
-        <v>624</v>
+        <v>392</v>
       </c>
       <c r="F9" t="n">
-        <v>419</v>
+        <v>312</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1908,124 +1908,124 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>389</v>
+        <v>145</v>
       </c>
       <c r="M9" t="n">
-        <v>77</v>
+        <v>403</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>-2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.8</v>
+        <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2999999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="n">
-        <v>7.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.316</v>
+        <v>-2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3799999999999999</v>
+        <v>-2.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2.5</v>
+        <v>-6</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.800000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.6000000000000001</v>
+        <v>-0.0349999999999997</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.2999999999999998</v>
-      </c>
+        <v>-0.4700000000000002</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>-1.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AK9" t="n">
-        <v>73.29545454545455</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>72.99111111111111</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>4.902169421487613</v>
-      </c>
+        <v>80.13415404040404</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.03749999999999432</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>14692283.05785124</v>
+        <v>2.362852243863756</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.699896694214871</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+        <v>0.3619543532862792</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-238945.7190112025</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-112321.4285714291</v>
+      </c>
       <c r="AS9" t="n">
-        <v>2.517704458265484</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
-        <v>0.5102272727272728</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.7660123966942081</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
+        <v>0.1161873589842288</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.1089285714285715</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>3.742857142857105</v>
+      </c>
       <c r="AX9" t="n">
-        <v>1.409744653790366</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.375206611570235</v>
-      </c>
+        <v>0.9857142857142875</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>0.4238095238095236</v>
+        <v>-0.2910714285714278</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="n">
-        <v>3.202640962511481</v>
-      </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>2.96223784474266</v>
+        <v>0.9510967786844304</v>
       </c>
       <c r="BE9" t="n">
-        <v>10053627.24598238</v>
+        <v>0.9000830395087078</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
@@ -2089,101 +2089,101 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AA10" t="n">
         <v>0.25</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AB10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC10" t="n">
         <v>-0.1925000000000001</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AD10" t="n">
         <v>-1.3675</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-4</v>
       </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AI10" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AJ10" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AE10" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
         <v>78.65909090909091</v>
       </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
+      <c r="AM10" t="n">
         <v>-12.20606060606062</v>
       </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
+        <v>-0.06185875316307943</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-11.21757821486082</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-32647976.76558546</v>
+      </c>
+      <c r="AR10" t="n">
         <v>-45110909.09090909</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AS10" t="n">
+        <v>-0.8513400046008743</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-1.65050505050505</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-0.6909090909090878</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.4595959595959549</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
         <v>-11.28787878787877</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>-0.06185875316307943</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="n">
-        <v>-1.65050505050505</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.4595959595959549</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>1.938006096158269</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-0.6909090909090878</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.8513400046008743</v>
       </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
         <v>-10.60447435012652</v>
       </c>
-      <c r="BD10" t="n">
-        <v>-11.21757821486082</v>
-      </c>
       <c r="BE10" t="n">
-        <v>-32647976.76558546</v>
+        <v>1.938006096158269</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -2251,103 +2251,103 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AB11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC11" t="n">
         <v>0.8125</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AD11" t="n">
         <v>-0.08499999999999996</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI11" t="n">
         <v>-0.3999999999999999</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AJ11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="n">
-        <v>77.97987603305785</v>
+        <v>78.01627272727274</v>
       </c>
       <c r="AL11" t="n">
         <v>74.54545454545453</v>
       </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
+      <c r="AM11" t="n">
         <v>2.722746950019683</v>
       </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
+        <v>2.544944017851492</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5.024274162893079</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10984469.04336654</v>
+      </c>
+      <c r="AR11" t="n">
         <v>17019983.60225633</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AS11" t="n">
+        <v>0.5276486675638035</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.6762691853600942</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>0.7954742227468898</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-2.333989243080151</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
         <v>5.466745375836283</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
-        <v>2.544944017851492</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="n">
-        <v>0.6762691853600942</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-2.333989243080151</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>-3.654831907610326</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.7954742227468898</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.5276486675638035</v>
       </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="n">
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
         <v>0.02235611336402599</v>
       </c>
-      <c r="BD11" t="n">
-        <v>5.024274162893079</v>
-      </c>
       <c r="BE11" t="n">
-        <v>10984469.04336654</v>
+        <v>-3.654831907610326</v>
       </c>
       <c r="BF11" t="n">
         <v>0</v>
@@ -2415,103 +2415,103 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AB12" t="n">
         <v>4</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-7.333333333333333</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="AC12" t="n">
         <v>-0.3266666666666667</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AD12" t="n">
         <v>-1.066666666666667</v>
       </c>
-      <c r="Y12" t="n">
-        <v>5.666666666666664</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-5.666666666666664</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6.666666666666668</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AI12" t="n">
         <v>-2</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AJ12" t="n">
         <v>2</v>
       </c>
-      <c r="AE12" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
         <v>72.98888888888888</v>
       </c>
       <c r="AL12" t="n">
         <v>69</v>
       </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
+      <c r="AM12" t="n">
         <v>4.648877665544319</v>
       </c>
+      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
+        <v>0.8657106619825754</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.016572387689507</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3577584.255148304</v>
+      </c>
+      <c r="AR12" t="n">
         <v>6137873.176206509</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AS12" t="n">
+        <v>0.04603727455894635</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.1550505050505051</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>2.392087542087609</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-1.061503928170595</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
         <v>4.746520763187448</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="n">
-        <v>0.8657106619825754</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="n">
-        <v>0.1550505050505051</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-1.061503928170595</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>2.571972157433972</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>2.392087542087609</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.04603727455894635</v>
       </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="n">
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
         <v>7.331146766698879</v>
       </c>
-      <c r="BD12" t="n">
-        <v>3.016572387689507</v>
-      </c>
       <c r="BE12" t="n">
-        <v>3577584.255148304</v>
+        <v>2.571972157433972</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2520,23 +2520,23 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>45518.65625</v>
       </c>
       <c r="C13" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D13" t="n">
         <v>146</v>
       </c>
       <c r="E13" t="n">
-        <v>419</v>
+        <v>347</v>
       </c>
       <c r="F13" t="n">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2561,56 +2561,122 @@
         <v>428</v>
       </c>
       <c r="M13" t="n">
-        <v>434</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+        <v>236</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.665</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AG13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
       <c r="AK13" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>69.5409090909091</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.123376623376615</v>
+      </c>
       <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>-4.192364047068082</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.433221114532756</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1651013.664523781</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1776341.991341992</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.01481295416717421</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.09220779220779241</v>
+      </c>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>-3.160173160173173</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-2.962770562770565</v>
+      </c>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>4.493073593073603</v>
+      </c>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>4.043052003410054</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.0640253202730392</v>
+      </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
@@ -2618,23 +2684,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>45518.65625</v>
       </c>
       <c r="C14" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
       </c>
       <c r="E14" t="n">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="F14" t="n">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -2659,122 +2725,56 @@
         <v>428</v>
       </c>
       <c r="M14" t="n">
-        <v>236</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="n">
-        <v>71.18181818181819</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>69.5409090909091</v>
-      </c>
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="n">
-        <v>2.123376623376615</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1776341.991341992</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>4.493073593073603</v>
-      </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="n">
-        <v>-4.192364047068082</v>
-      </c>
+      <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="n">
-        <v>0.09220779220779241</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>-2.962770562770565</v>
-      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="n">
-        <v>0.0640253202730392</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>-3.160173160173173</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.01481295416717421</v>
-      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="n">
-        <v>4.043052003410054</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.433221114532756</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1651013.664523781</v>
-      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>45517.66666666666</v>
       </c>
       <c r="C15" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D15" t="n">
         <v>146</v>
@@ -2823,7 +2823,7 @@
         <v>110</v>
       </c>
       <c r="M15" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -2880,23 +2880,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C16" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D16" t="n">
         <v>146</v>
       </c>
       <c r="E16" t="n">
-        <v>781</v>
+        <v>245</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>441</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="M16" t="n">
-        <v>168</v>
+        <v>436</v>
       </c>
       <c r="N16" t="n">
         <v>-2</v>
@@ -2952,10 +2952,10 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AK16" t="n">
+        <v>69.13636363636363</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
@@ -2982,23 +2982,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C17" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D17" t="n">
         <v>146</v>
       </c>
       <c r="E17" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F17" t="n">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -3020,17 +3020,17 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="M17" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N17" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
@@ -3055,7 +3055,7 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="n">
-        <v>69.13636363636363</v>
+        <v>69.2</v>
       </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -3084,23 +3084,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C18" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D18" t="n">
         <v>146</v>
       </c>
       <c r="E18" t="n">
-        <v>436</v>
+        <v>740</v>
       </c>
       <c r="F18" t="n">
-        <v>734</v>
+        <v>412</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -3122,57 +3122,125 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>435</v>
+        <v>331</v>
       </c>
       <c r="M18" t="n">
-        <v>434</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>236</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-21</v>
+      </c>
+      <c r="V18" t="n">
+        <v>21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.73</v>
+      </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AG18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>74</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>69</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.3376984126984013</v>
+      </c>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>0.2953982603720817</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.5411850373547225</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-130365.5393059938</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-1281253.306878306</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>1.906944444444434</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.621296296296293</v>
+      </c>
       <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>-5.914153439153438</v>
+      </c>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>0.4217652273900256</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.216519796764572</v>
+      </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
@@ -3180,23 +3248,23 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C19" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D19" t="n">
         <v>146</v>
       </c>
       <c r="E19" t="n">
-        <v>399</v>
+        <v>781</v>
       </c>
       <c r="F19" t="n">
-        <v>542</v>
+        <v>93</v>
       </c>
       <c r="G19" t="n">
         <v>48</v>
@@ -3218,14 +3286,18 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M19" t="n">
-        <v>434</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-2</v>
+      </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
@@ -3249,7 +3321,9 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
@@ -3283,7 +3357,7 @@
         <v>45517.65625</v>
       </c>
       <c r="C20" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D20" t="n">
         <v>146</v>
@@ -3314,10 +3388,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M20" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3376,23 +3450,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C21" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D21" t="n">
         <v>146</v>
       </c>
       <c r="E21" t="n">
-        <v>233</v>
+        <v>540</v>
       </c>
       <c r="F21" t="n">
-        <v>426</v>
+        <v>148</v>
       </c>
       <c r="G21" t="n">
         <v>48</v>
@@ -3414,18 +3488,14 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="M21" t="n">
-        <v>434</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
@@ -3448,9 +3518,7 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="n">
-        <v>69.2</v>
-      </c>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
@@ -3478,23 +3546,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C22" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D22" t="n">
         <v>146</v>
       </c>
       <c r="E22" t="n">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F22" t="n">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="G22" t="n">
         <v>48</v>
@@ -3516,23 +3584,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>347</v>
+        <v>437</v>
       </c>
       <c r="M22" t="n">
-        <v>434</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-1</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3554,9 +3614,7 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
@@ -3584,23 +3642,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C23" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D23" t="n">
         <v>146</v>
       </c>
       <c r="E23" t="n">
-        <v>566</v>
+        <v>278</v>
       </c>
       <c r="F23" t="n">
-        <v>540</v>
+        <v>376</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -3622,14 +3680,18 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M23" t="n">
-        <v>434</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>436</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>0</v>
@@ -3680,23 +3742,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C24" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D24" t="n">
         <v>146</v>
       </c>
       <c r="E24" t="n">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>501</v>
       </c>
       <c r="G24" t="n">
         <v>48</v>
@@ -3718,19 +3780,23 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="M24" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1</v>
+      </c>
       <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1</v>
+      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -3753,7 +3819,7 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="n">
-        <v>70.70833333333333</v>
+        <v>69.64141414141415</v>
       </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
@@ -3782,23 +3848,23 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C25" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D25" t="n">
         <v>146</v>
       </c>
       <c r="E25" t="n">
-        <v>555</v>
+        <v>436</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>734</v>
       </c>
       <c r="G25" t="n">
         <v>48</v>
@@ -3820,10 +3886,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M25" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -3878,23 +3944,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C26" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D26" t="n">
         <v>146</v>
       </c>
       <c r="E26" t="n">
-        <v>278</v>
+        <v>182</v>
       </c>
       <c r="F26" t="n">
-        <v>376</v>
+        <v>185</v>
       </c>
       <c r="G26" t="n">
         <v>48</v>
@@ -3916,18 +3982,18 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M26" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
         <v>0</v>
@@ -3978,23 +4044,23 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C27" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D27" t="n">
         <v>146</v>
       </c>
       <c r="E27" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="F27" t="n">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -4016,10 +4082,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M27" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -4074,23 +4140,23 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C28" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D28" t="n">
         <v>146</v>
       </c>
       <c r="E28" t="n">
-        <v>182</v>
+        <v>566</v>
       </c>
       <c r="F28" t="n">
-        <v>185</v>
+        <v>540</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -4112,17 +4178,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M28" t="n">
-        <v>434</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
@@ -4174,23 +4236,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C29" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D29" t="n">
         <v>146</v>
       </c>
       <c r="E29" t="n">
-        <v>740</v>
+        <v>338</v>
       </c>
       <c r="F29" t="n">
-        <v>412</v>
+        <v>125</v>
       </c>
       <c r="G29" t="n">
         <v>48</v>
@@ -4212,125 +4274,63 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>331</v>
+        <v>73</v>
       </c>
       <c r="M29" t="n">
-        <v>236</v>
+        <v>436</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>-6</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>-21</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2</v>
-      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="n">
-        <v>74</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>69</v>
-      </c>
+        <v>70.70833333333333</v>
+      </c>
+      <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="n">
-        <v>0.3376984126984013</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>-1281253.306878306</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-5.914153439153438</v>
-      </c>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="n">
-        <v>0.2953982603720817</v>
-      </c>
+      <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.621296296296293</v>
-      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
       <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="n">
-        <v>1.216519796764572</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.906944444444434</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="n">
-        <v>0.4217652273900256</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>-0.5411850373547225</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>-130365.5393059938</v>
-      </c>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="n">
         <v>0</v>
       </c>
@@ -4338,23 +4338,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C30" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D30" t="n">
         <v>146</v>
       </c>
       <c r="E30" t="n">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="F30" t="n">
-        <v>368</v>
+        <v>473</v>
       </c>
       <c r="G30" t="n">
         <v>48</v>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M30" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -4434,23 +4434,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C31" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D31" t="n">
         <v>146</v>
       </c>
       <c r="E31" t="n">
-        <v>621</v>
+        <v>684</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="G31" t="n">
         <v>48</v>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M31" t="n">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -4503,7 +4503,9 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>72.22962962962963</v>
+      </c>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
@@ -4530,23 +4532,23 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C32" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D32" t="n">
         <v>146</v>
       </c>
       <c r="E32" t="n">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="F32" t="n">
-        <v>488</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
         <v>48</v>
@@ -4568,10 +4570,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M32" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -4626,23 +4628,23 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C33" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D33" t="n">
         <v>146</v>
       </c>
       <c r="E33" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="F33" t="n">
-        <v>473</v>
+        <v>194</v>
       </c>
       <c r="G33" t="n">
         <v>48</v>
@@ -4664,57 +4666,125 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="M33" t="n">
-        <v>434</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-21</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
+      <c r="AG33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-2.816666666666649</v>
+      </c>
       <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>-0.2023692810457476</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-2.49301163447835</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>-1269591.292981506</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>-2234641.203703703</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
       <c r="AU33" t="inlineStr"/>
       <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
+      <c r="AW33" t="n">
+        <v>-1.420370370370335</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>-0.5010416666666657</v>
+      </c>
       <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
+      <c r="AZ33" t="n">
+        <v>-2.82534722222222</v>
+      </c>
       <c r="BA33" t="inlineStr"/>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
+      <c r="BD33" t="n">
+        <v>-2.202103660443441</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.301905073233439</v>
+      </c>
       <c r="BF33" t="n">
         <v>0</v>
       </c>
@@ -4729,7 +4799,7 @@
         <v>45517.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D34" t="n">
         <v>146</v>
@@ -4760,10 +4830,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M34" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -4818,23 +4888,23 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C35" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D35" t="n">
         <v>146</v>
       </c>
       <c r="E35" t="n">
-        <v>764</v>
+        <v>243</v>
       </c>
       <c r="F35" t="n">
-        <v>790</v>
+        <v>368</v>
       </c>
       <c r="G35" t="n">
         <v>48</v>
@@ -4856,10 +4926,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>346</v>
+        <v>437</v>
       </c>
       <c r="M35" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -4886,9 +4956,7 @@
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="n">
-        <v>69.33522727272728</v>
-      </c>
+      <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
@@ -4916,23 +4984,23 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C36" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D36" t="n">
         <v>146</v>
       </c>
       <c r="E36" t="n">
-        <v>273</v>
+        <v>528</v>
       </c>
       <c r="F36" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G36" t="n">
         <v>48</v>
@@ -4954,125 +5022,59 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="M36" t="n">
-        <v>209</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>7</v>
-      </c>
-      <c r="V36" t="n">
-        <v>-24</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X36" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>70.18181818181819</v>
-      </c>
+        <v>71.47727272727272</v>
+      </c>
+      <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="n">
-        <v>-2.816666666666649</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>-2234641.203703703</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>-2.82534722222222</v>
-      </c>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="n">
-        <v>-0.2023692810457476</v>
-      </c>
+      <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>-0.5010416666666657</v>
-      </c>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="n">
-        <v>1.301905073233439</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>-1.420370370370335</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="n">
-        <v>-2.202103660443441</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>-2.49301163447835</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>-1269591.292981506</v>
-      </c>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
       <c r="BF36" t="n">
         <v>0</v>
       </c>
@@ -5080,23 +5082,23 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C37" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D37" t="n">
         <v>146</v>
       </c>
       <c r="E37" t="n">
-        <v>684</v>
+        <v>621</v>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
         <v>48</v>
@@ -5118,10 +5120,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M37" t="n">
-        <v>333</v>
+        <v>436</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -5149,9 +5151,7 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M38" t="n">
         <v>175</v>
@@ -5280,23 +5280,23 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C39" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D39" t="n">
         <v>146</v>
       </c>
       <c r="E39" t="n">
-        <v>756</v>
+        <v>228</v>
       </c>
       <c r="F39" t="n">
-        <v>181</v>
+        <v>488</v>
       </c>
       <c r="G39" t="n">
         <v>48</v>
@@ -5318,18 +5318,14 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M39" t="n">
-        <v>434</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-2</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
         <v>0</v>
@@ -5380,23 +5376,23 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C40" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D40" t="n">
         <v>146</v>
       </c>
       <c r="E40" t="n">
-        <v>528</v>
+        <v>325</v>
       </c>
       <c r="F40" t="n">
-        <v>191</v>
+        <v>759</v>
       </c>
       <c r="G40" t="n">
         <v>48</v>
@@ -5418,10 +5414,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="M40" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -5448,9 +5444,7 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
@@ -5478,23 +5472,23 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C41" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D41" t="n">
         <v>146</v>
       </c>
       <c r="E41" t="n">
-        <v>590</v>
+        <v>756</v>
       </c>
       <c r="F41" t="n">
-        <v>600</v>
+        <v>181</v>
       </c>
       <c r="G41" t="n">
         <v>48</v>
@@ -5516,14 +5510,18 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M41" t="n">
-        <v>209</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
+        <v>436</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-2</v>
+      </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>0</v>
@@ -5547,9 +5545,7 @@
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="n">
-        <v>71.77777777777777</v>
-      </c>
+      <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
@@ -5576,23 +5572,23 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C42" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D42" t="n">
         <v>146</v>
       </c>
       <c r="E42" t="n">
-        <v>307</v>
+        <v>764</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>790</v>
       </c>
       <c r="G42" t="n">
         <v>48</v>
@@ -5614,10 +5610,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>435</v>
+        <v>346</v>
       </c>
       <c r="M42" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -5644,7 +5640,9 @@
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
+      <c r="AK42" t="n">
+        <v>69.33522727272728</v>
+      </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
@@ -5672,23 +5670,23 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
       <c r="C43" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D43" t="n">
         <v>146</v>
       </c>
       <c r="E43" t="n">
-        <v>325</v>
+        <v>590</v>
       </c>
       <c r="F43" t="n">
-        <v>759</v>
+        <v>600</v>
       </c>
       <c r="G43" t="n">
         <v>48</v>
@@ -5710,10 +5708,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M43" t="n">
-        <v>434</v>
+        <v>209</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -5741,7 +5739,9 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M44" t="n">
         <v>221</v>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M45" t="n">
         <v>278</v>
@@ -5971,7 +5971,7 @@
         <v>45517.64583333334</v>
       </c>
       <c r="C46" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D46" t="n">
         <v>146</v>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M46" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -6119,103 +6119,103 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>7</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
         <v>0.75</v>
       </c>
-      <c r="U47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W47" t="n">
+      <c r="AC47" t="n">
         <v>0.1174999999999999</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AD47" t="n">
         <v>0.5950000000000002</v>
       </c>
-      <c r="Y47" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI47" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AJ47" t="n">
         <v>1</v>
       </c>
-      <c r="AE47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="n">
         <v>76.15625</v>
       </c>
       <c r="AL47" t="n">
         <v>77.36540404040404</v>
       </c>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="n">
-        <v>-5.467217630854009</v>
-      </c>
+      <c r="AM47" t="n">
+        <v>-5.649201101928398</v>
+      </c>
+      <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="n">
-        <v>-42477277.31864096</v>
+        <v>5.572761884128397</v>
       </c>
       <c r="AP47" t="n">
-        <v>-3.063360881542692</v>
-      </c>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
+        <v>-3.786451794156378</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>-27821847.68622385</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>-43592483.9302112</v>
+      </c>
       <c r="AS47" t="n">
-        <v>5.571349283515019</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="n">
-        <v>-0.8917355371900828</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>-1.708723599632687</v>
-      </c>
-      <c r="AW47" t="inlineStr"/>
+        <v>-0.4920997390452169</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>-0.9389256198347109</v>
+      </c>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="n">
+        <v>2.633526170798888</v>
+      </c>
       <c r="AX47" t="n">
-        <v>-0.6278392923824185</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>2.907988980716226</v>
-      </c>
+        <v>-1.885417814508717</v>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="n">
-        <v>-0.4772401918007592</v>
+        <v>-3.136501377410468</v>
       </c>
       <c r="BA47" t="inlineStr"/>
       <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="n">
-        <v>-5.534005271769757</v>
-      </c>
+      <c r="BC47" t="inlineStr"/>
       <c r="BD47" t="n">
-        <v>-3.686012020091297</v>
+        <v>-5.74893747653573</v>
       </c>
       <c r="BE47" t="n">
-        <v>-27542234.39953895</v>
+        <v>-0.6387726578234556</v>
       </c>
       <c r="BF47" t="n">
         <v>1</v>
